--- a/main_data/evolucion_vinculacion_y_uso_wompi_vinc_primer_regi.xlsx
+++ b/main_data/evolucion_vinculacion_y_uso_wompi_vinc_primer_regi.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,2281 +497,2367 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>202605</v>
+        <v>202607</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7220</v>
+        <v>7839</v>
       </c>
       <c r="D2" t="n">
-        <v>32553</v>
+        <v>47146</v>
       </c>
       <c r="E2" t="n">
-        <v>121308</v>
+        <v>135772</v>
       </c>
       <c r="F2" t="n">
-        <v>112313</v>
+        <v>112164</v>
       </c>
       <c r="G2" t="n">
-        <v>144866</v>
+        <v>159310</v>
       </c>
       <c r="H2" t="n">
-        <v>1209</v>
+        <v>1645</v>
       </c>
       <c r="I2" t="n">
-        <v>19409</v>
+        <v>21208</v>
       </c>
       <c r="J2" t="n">
-        <v>27048</v>
+        <v>34124</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0371</v>
+        <v>0.0349</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1728</v>
+        <v>0.1891</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1867</v>
+        <v>0.2142</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>202604</v>
+        <v>202606</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20260401</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7816</v>
+        <v>6988</v>
       </c>
       <c r="D3" t="n">
-        <v>25333</v>
+        <v>39307</v>
       </c>
       <c r="E3" t="n">
-        <v>114088</v>
+        <v>127933</v>
       </c>
       <c r="F3" t="n">
-        <v>112313</v>
+        <v>112164</v>
       </c>
       <c r="G3" t="n">
-        <v>137646</v>
+        <v>151471</v>
       </c>
       <c r="H3" t="n">
-        <v>1120</v>
+        <v>1128</v>
       </c>
       <c r="I3" t="n">
-        <v>18262</v>
+        <v>20297</v>
       </c>
       <c r="J3" t="n">
-        <v>23595</v>
+        <v>30139</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0442</v>
+        <v>0.0287</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1626</v>
+        <v>0.181</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1714</v>
+        <v>0.199</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>202603</v>
+        <v>202605</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20260301</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7124</v>
+        <v>7204</v>
       </c>
       <c r="D4" t="n">
-        <v>17517</v>
+        <v>32319</v>
       </c>
       <c r="E4" t="n">
-        <v>106272</v>
+        <v>120945</v>
       </c>
       <c r="F4" t="n">
-        <v>112313</v>
+        <v>112164</v>
       </c>
       <c r="G4" t="n">
-        <v>129830</v>
+        <v>144483</v>
       </c>
       <c r="H4" t="n">
-        <v>974</v>
+        <v>1200</v>
       </c>
       <c r="I4" t="n">
-        <v>16942</v>
+        <v>19366</v>
       </c>
       <c r="J4" t="n">
-        <v>20174</v>
+        <v>26945</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0556</v>
+        <v>0.0371</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1508</v>
+        <v>0.1727</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1554</v>
+        <v>0.1865</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>202602</v>
+        <v>202604</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20260201</t>
+          <t>20260401</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5692</v>
+        <v>7681</v>
       </c>
       <c r="D5" t="n">
-        <v>10393</v>
+        <v>25115</v>
       </c>
       <c r="E5" t="n">
-        <v>99148</v>
+        <v>113741</v>
       </c>
       <c r="F5" t="n">
-        <v>112313</v>
+        <v>112164</v>
       </c>
       <c r="G5" t="n">
-        <v>122706</v>
+        <v>137279</v>
       </c>
       <c r="H5" t="n">
-        <v>718</v>
+        <v>1100</v>
       </c>
       <c r="I5" t="n">
-        <v>15033</v>
+        <v>18226</v>
       </c>
       <c r="J5" t="n">
-        <v>16694</v>
+        <v>23516</v>
       </c>
       <c r="K5" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.0438</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1338</v>
+        <v>0.1625</v>
       </c>
       <c r="M5" t="n">
-        <v>0.136</v>
+        <v>0.1713</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>202601</v>
+        <v>202603</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20260101</t>
+          <t>20260301</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4701</v>
+        <v>7054</v>
       </c>
       <c r="D6" t="n">
-        <v>4701</v>
+        <v>17434</v>
       </c>
       <c r="E6" t="n">
-        <v>93456</v>
+        <v>106060</v>
       </c>
       <c r="F6" t="n">
-        <v>112313</v>
+        <v>112164</v>
       </c>
       <c r="G6" t="n">
-        <v>117014</v>
+        <v>129598</v>
       </c>
       <c r="H6" t="n">
-        <v>560</v>
+        <v>959</v>
       </c>
       <c r="I6" t="n">
-        <v>12275</v>
+        <v>16906</v>
       </c>
       <c r="J6" t="n">
-        <v>12835</v>
+        <v>20119</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1191</v>
+        <v>0.055</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1093</v>
+        <v>0.1507</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1097</v>
+        <v>0.1552</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>202512</v>
+        <v>202602</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20251201</t>
+          <t>20260201</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4245</v>
+        <v>5684</v>
       </c>
       <c r="D7" t="n">
-        <v>40793</v>
+        <v>10380</v>
       </c>
       <c r="E7" t="n">
-        <v>88755</v>
+        <v>99006</v>
       </c>
       <c r="F7" t="n">
-        <v>71520</v>
+        <v>112164</v>
       </c>
       <c r="G7" t="n">
-        <v>112313</v>
+        <v>122544</v>
       </c>
       <c r="H7" t="n">
-        <v>553</v>
+        <v>714</v>
       </c>
       <c r="I7" t="n">
-        <v>17377</v>
+        <v>15002</v>
       </c>
       <c r="J7" t="n">
-        <v>28209</v>
+        <v>16662</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0136</v>
+        <v>0.0688</v>
       </c>
       <c r="L7" t="n">
-        <v>0.243</v>
+        <v>0.1338</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2512</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>202511</v>
+        <v>202601</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20251101</t>
+          <t>20260101</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4654</v>
+        <v>4696</v>
       </c>
       <c r="D8" t="n">
-        <v>36548</v>
+        <v>4696</v>
       </c>
       <c r="E8" t="n">
-        <v>84510</v>
+        <v>93322</v>
       </c>
       <c r="F8" t="n">
-        <v>71520</v>
+        <v>112164</v>
       </c>
       <c r="G8" t="n">
-        <v>108068</v>
+        <v>116860</v>
       </c>
       <c r="H8" t="n">
-        <v>583</v>
+        <v>565</v>
       </c>
       <c r="I8" t="n">
-        <v>17109</v>
+        <v>12252</v>
       </c>
       <c r="J8" t="n">
-        <v>26698</v>
+        <v>12817</v>
       </c>
       <c r="K8" t="n">
-        <v>0.016</v>
+        <v>0.1203</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2392</v>
+        <v>0.1092</v>
       </c>
       <c r="M8" t="n">
-        <v>0.247</v>
+        <v>0.1097</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20251001</t>
+          <t>20251201</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4887</v>
+        <v>4244</v>
       </c>
       <c r="D9" t="n">
-        <v>31894</v>
+        <v>40753</v>
       </c>
       <c r="E9" t="n">
-        <v>79856</v>
+        <v>88626</v>
       </c>
       <c r="F9" t="n">
-        <v>71520</v>
+        <v>71411</v>
       </c>
       <c r="G9" t="n">
-        <v>103414</v>
+        <v>112164</v>
       </c>
       <c r="H9" t="n">
-        <v>574</v>
+        <v>556</v>
       </c>
       <c r="I9" t="n">
-        <v>16811</v>
+        <v>17336</v>
       </c>
       <c r="J9" t="n">
-        <v>25126</v>
+        <v>28149</v>
       </c>
       <c r="K9" t="n">
-        <v>0.018</v>
+        <v>0.0136</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2351</v>
+        <v>0.2428</v>
       </c>
       <c r="M9" t="n">
-        <v>0.243</v>
+        <v>0.251</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>202509</v>
+        <v>202511</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20250901</t>
+          <t>20251101</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4485</v>
+        <v>4653</v>
       </c>
       <c r="D10" t="n">
-        <v>27007</v>
+        <v>36509</v>
       </c>
       <c r="E10" t="n">
-        <v>74969</v>
+        <v>84382</v>
       </c>
       <c r="F10" t="n">
-        <v>71520</v>
+        <v>71411</v>
       </c>
       <c r="G10" t="n">
-        <v>98527</v>
+        <v>107920</v>
       </c>
       <c r="H10" t="n">
-        <v>543</v>
+        <v>582</v>
       </c>
       <c r="I10" t="n">
-        <v>16460</v>
+        <v>17068</v>
       </c>
       <c r="J10" t="n">
-        <v>23534</v>
+        <v>26634</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0201</v>
+        <v>0.0159</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2301</v>
+        <v>0.239</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2389</v>
+        <v>0.2468</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>202508</v>
+        <v>202510</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20250801</t>
+          <t>20251001</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4268</v>
+        <v>4879</v>
       </c>
       <c r="D11" t="n">
-        <v>22522</v>
+        <v>31856</v>
       </c>
       <c r="E11" t="n">
-        <v>70484</v>
+        <v>79729</v>
       </c>
       <c r="F11" t="n">
-        <v>71520</v>
+        <v>71411</v>
       </c>
       <c r="G11" t="n">
-        <v>94042</v>
+        <v>103267</v>
       </c>
       <c r="H11" t="n">
-        <v>458</v>
+        <v>570</v>
       </c>
       <c r="I11" t="n">
-        <v>16066</v>
+        <v>16769</v>
       </c>
       <c r="J11" t="n">
-        <v>21973</v>
+        <v>25066</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0203</v>
+        <v>0.0179</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2246</v>
+        <v>0.2348</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2337</v>
+        <v>0.2427</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>202507</v>
+        <v>202509</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>20250701</t>
+          <t>20250901</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4306</v>
+        <v>4479</v>
       </c>
       <c r="D12" t="n">
-        <v>18254</v>
+        <v>26977</v>
       </c>
       <c r="E12" t="n">
-        <v>66216</v>
+        <v>74850</v>
       </c>
       <c r="F12" t="n">
-        <v>71520</v>
+        <v>71411</v>
       </c>
       <c r="G12" t="n">
-        <v>89774</v>
+        <v>98388</v>
       </c>
       <c r="H12" t="n">
-        <v>627</v>
+        <v>542</v>
       </c>
       <c r="I12" t="n">
-        <v>15620</v>
+        <v>16420</v>
       </c>
       <c r="J12" t="n">
-        <v>20477</v>
+        <v>23482</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0343</v>
+        <v>0.0201</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2184</v>
+        <v>0.2299</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2281</v>
+        <v>0.2387</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>202506</v>
+        <v>202508</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20250601</t>
+          <t>20250801</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3232</v>
+        <v>4263</v>
       </c>
       <c r="D13" t="n">
-        <v>13948</v>
+        <v>22498</v>
       </c>
       <c r="E13" t="n">
-        <v>61910</v>
+        <v>70371</v>
       </c>
       <c r="F13" t="n">
-        <v>71520</v>
+        <v>71411</v>
       </c>
       <c r="G13" t="n">
-        <v>85468</v>
+        <v>93909</v>
       </c>
       <c r="H13" t="n">
-        <v>375</v>
+        <v>458</v>
       </c>
       <c r="I13" t="n">
-        <v>15135</v>
+        <v>16028</v>
       </c>
       <c r="J13" t="n">
-        <v>18844</v>
+        <v>21925</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0269</v>
+        <v>0.0204</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2116</v>
+        <v>0.2244</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2205</v>
+        <v>0.2335</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>202505</v>
+        <v>202507</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20250501</t>
+          <t>20250701</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3259</v>
+        <v>4305</v>
       </c>
       <c r="D14" t="n">
-        <v>10716</v>
+        <v>18235</v>
       </c>
       <c r="E14" t="n">
-        <v>58678</v>
+        <v>66108</v>
       </c>
       <c r="F14" t="n">
-        <v>71520</v>
+        <v>71411</v>
       </c>
       <c r="G14" t="n">
-        <v>82236</v>
+        <v>89646</v>
       </c>
       <c r="H14" t="n">
-        <v>503</v>
+        <v>625</v>
       </c>
       <c r="I14" t="n">
-        <v>14595</v>
+        <v>15583</v>
       </c>
       <c r="J14" t="n">
-        <v>17498</v>
+        <v>20431</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0469</v>
+        <v>0.0343</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2041</v>
+        <v>0.2182</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2128</v>
+        <v>0.2279</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>202504</v>
+        <v>202506</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20250401</t>
+          <t>20250601</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1983</v>
+        <v>3230</v>
       </c>
       <c r="D15" t="n">
-        <v>7457</v>
+        <v>13930</v>
       </c>
       <c r="E15" t="n">
-        <v>55419</v>
+        <v>61803</v>
       </c>
       <c r="F15" t="n">
-        <v>71520</v>
+        <v>71411</v>
       </c>
       <c r="G15" t="n">
-        <v>78977</v>
+        <v>85341</v>
       </c>
       <c r="H15" t="n">
-        <v>251</v>
+        <v>375</v>
       </c>
       <c r="I15" t="n">
-        <v>13736</v>
+        <v>15099</v>
       </c>
       <c r="J15" t="n">
-        <v>15637</v>
+        <v>18801</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0337</v>
+        <v>0.0269</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1921</v>
+        <v>0.2114</v>
       </c>
       <c r="M15" t="n">
-        <v>0.198</v>
+        <v>0.2203</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>202503</v>
+        <v>202505</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20250301</t>
+          <t>20250501</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2020</v>
+        <v>3260</v>
       </c>
       <c r="D16" t="n">
-        <v>5474</v>
+        <v>10700</v>
       </c>
       <c r="E16" t="n">
-        <v>53436</v>
+        <v>58573</v>
       </c>
       <c r="F16" t="n">
-        <v>71520</v>
+        <v>71411</v>
       </c>
       <c r="G16" t="n">
-        <v>76994</v>
+        <v>82111</v>
       </c>
       <c r="H16" t="n">
-        <v>260</v>
+        <v>503</v>
       </c>
       <c r="I16" t="n">
-        <v>12848</v>
+        <v>14560</v>
       </c>
       <c r="J16" t="n">
-        <v>14167</v>
+        <v>17457</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0475</v>
+        <v>0.047</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1796</v>
+        <v>0.2039</v>
       </c>
       <c r="M16" t="n">
-        <v>0.184</v>
+        <v>0.2126</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>202502</v>
+        <v>202504</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20250201</t>
+          <t>20250401</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1723</v>
+        <v>1979</v>
       </c>
       <c r="D17" t="n">
-        <v>3454</v>
+        <v>7440</v>
       </c>
       <c r="E17" t="n">
-        <v>51416</v>
+        <v>55313</v>
       </c>
       <c r="F17" t="n">
-        <v>71520</v>
+        <v>71411</v>
       </c>
       <c r="G17" t="n">
-        <v>74974</v>
+        <v>78851</v>
       </c>
       <c r="H17" t="n">
-        <v>302</v>
+        <v>250</v>
       </c>
       <c r="I17" t="n">
-        <v>11585</v>
+        <v>13701</v>
       </c>
       <c r="J17" t="n">
-        <v>12380</v>
+        <v>15597</v>
       </c>
       <c r="K17" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.0336</v>
       </c>
       <c r="L17" t="n">
-        <v>0.162</v>
+        <v>0.1919</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1651</v>
+        <v>0.1978</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>202501</v>
+        <v>202503</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>20250101</t>
+          <t>20250301</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1731</v>
+        <v>2016</v>
       </c>
       <c r="D18" t="n">
-        <v>1731</v>
+        <v>5461</v>
       </c>
       <c r="E18" t="n">
-        <v>49693</v>
+        <v>53334</v>
       </c>
       <c r="F18" t="n">
-        <v>71520</v>
+        <v>71411</v>
       </c>
       <c r="G18" t="n">
-        <v>73251</v>
+        <v>76872</v>
       </c>
       <c r="H18" t="n">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="I18" t="n">
-        <v>9513</v>
+        <v>12813</v>
       </c>
       <c r="J18" t="n">
-        <v>9833</v>
+        <v>14128</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1849</v>
+        <v>0.0476</v>
       </c>
       <c r="L18" t="n">
-        <v>0.133</v>
+        <v>0.1794</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1342</v>
+        <v>0.1838</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>202412</v>
+        <v>202502</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20241201</t>
+          <t>20250201</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1672</v>
+        <v>1717</v>
       </c>
       <c r="D19" t="n">
-        <v>24472</v>
+        <v>3445</v>
       </c>
       <c r="E19" t="n">
-        <v>47962</v>
+        <v>51318</v>
       </c>
       <c r="F19" t="n">
-        <v>47048</v>
+        <v>71411</v>
       </c>
       <c r="G19" t="n">
-        <v>71520</v>
+        <v>74856</v>
       </c>
       <c r="H19" t="n">
-        <v>318</v>
+        <v>302</v>
       </c>
       <c r="I19" t="n">
-        <v>13232</v>
+        <v>11551</v>
       </c>
       <c r="J19" t="n">
-        <v>21618</v>
+        <v>12345</v>
       </c>
       <c r="K19" t="n">
-        <v>0.013</v>
+        <v>0.0877</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2812</v>
+        <v>0.1618</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3023</v>
+        <v>0.1649</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>202411</v>
+        <v>202501</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20241101</t>
+          <t>20250101</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2322</v>
+        <v>1728</v>
       </c>
       <c r="D20" t="n">
-        <v>22800</v>
+        <v>1728</v>
       </c>
       <c r="E20" t="n">
-        <v>46290</v>
+        <v>49601</v>
       </c>
       <c r="F20" t="n">
-        <v>47048</v>
+        <v>71411</v>
       </c>
       <c r="G20" t="n">
-        <v>69848</v>
+        <v>73139</v>
       </c>
       <c r="H20" t="n">
-        <v>398</v>
+        <v>319</v>
       </c>
       <c r="I20" t="n">
-        <v>13020</v>
+        <v>9485</v>
       </c>
       <c r="J20" t="n">
-        <v>20537</v>
+        <v>9804</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0175</v>
+        <v>0.1846</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2767</v>
+        <v>0.1328</v>
       </c>
       <c r="M20" t="n">
-        <v>0.294</v>
+        <v>0.134</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>202410</v>
+        <v>202412</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20241001</t>
+          <t>20241201</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2611</v>
+        <v>1667</v>
       </c>
       <c r="D21" t="n">
-        <v>20478</v>
+        <v>24407</v>
       </c>
       <c r="E21" t="n">
-        <v>43968</v>
+        <v>47873</v>
       </c>
       <c r="F21" t="n">
-        <v>47048</v>
+        <v>47004</v>
       </c>
       <c r="G21" t="n">
-        <v>67526</v>
+        <v>71411</v>
       </c>
       <c r="H21" t="n">
-        <v>395</v>
+        <v>316</v>
       </c>
       <c r="I21" t="n">
-        <v>12771</v>
+        <v>13215</v>
       </c>
       <c r="J21" t="n">
-        <v>19229</v>
+        <v>21568</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0193</v>
+        <v>0.0129</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2714</v>
+        <v>0.2811</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2848</v>
+        <v>0.302</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>202409</v>
+        <v>202411</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20240901</t>
+          <t>20241101</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2437</v>
+        <v>2316</v>
       </c>
       <c r="D22" t="n">
-        <v>17867</v>
+        <v>22740</v>
       </c>
       <c r="E22" t="n">
-        <v>41357</v>
+        <v>46206</v>
       </c>
       <c r="F22" t="n">
-        <v>47048</v>
+        <v>47004</v>
       </c>
       <c r="G22" t="n">
-        <v>64915</v>
+        <v>69744</v>
       </c>
       <c r="H22" t="n">
-        <v>318</v>
+        <v>398</v>
       </c>
       <c r="I22" t="n">
-        <v>12489</v>
+        <v>13003</v>
       </c>
       <c r="J22" t="n">
-        <v>18050</v>
+        <v>20490</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0178</v>
+        <v>0.0175</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2655</v>
+        <v>0.2766</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2781</v>
+        <v>0.2938</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>202408</v>
+        <v>202410</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20240801</t>
+          <t>20241001</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2217</v>
+        <v>2602</v>
       </c>
       <c r="D23" t="n">
-        <v>15430</v>
+        <v>20424</v>
       </c>
       <c r="E23" t="n">
-        <v>38920</v>
+        <v>43890</v>
       </c>
       <c r="F23" t="n">
-        <v>47048</v>
+        <v>47004</v>
       </c>
       <c r="G23" t="n">
-        <v>62478</v>
+        <v>67428</v>
       </c>
       <c r="H23" t="n">
-        <v>315</v>
+        <v>392</v>
       </c>
       <c r="I23" t="n">
-        <v>12184</v>
+        <v>12755</v>
       </c>
       <c r="J23" t="n">
-        <v>16959</v>
+        <v>19186</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0204</v>
+        <v>0.0192</v>
       </c>
       <c r="L23" t="n">
-        <v>0.259</v>
+        <v>0.2714</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2714</v>
+        <v>0.2845</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>202407</v>
+        <v>202409</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20240701</t>
+          <t>20240901</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2002</v>
+        <v>2428</v>
       </c>
       <c r="D24" t="n">
-        <v>13213</v>
+        <v>17822</v>
       </c>
       <c r="E24" t="n">
-        <v>36703</v>
+        <v>41288</v>
       </c>
       <c r="F24" t="n">
-        <v>47048</v>
+        <v>47004</v>
       </c>
       <c r="G24" t="n">
-        <v>60261</v>
+        <v>64826</v>
       </c>
       <c r="H24" t="n">
-        <v>288</v>
+        <v>315</v>
       </c>
       <c r="I24" t="n">
-        <v>11819</v>
+        <v>12473</v>
       </c>
       <c r="J24" t="n">
-        <v>15857</v>
+        <v>18013</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0218</v>
+        <v>0.0177</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2512</v>
+        <v>0.2654</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2631</v>
+        <v>0.2779</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>202406</v>
+        <v>202408</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20240601</t>
+          <t>20240801</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1818</v>
+        <v>2216</v>
       </c>
       <c r="D25" t="n">
-        <v>11211</v>
+        <v>15394</v>
       </c>
       <c r="E25" t="n">
-        <v>34701</v>
+        <v>38860</v>
       </c>
       <c r="F25" t="n">
-        <v>47048</v>
+        <v>47004</v>
       </c>
       <c r="G25" t="n">
-        <v>58259</v>
+        <v>62398</v>
       </c>
       <c r="H25" t="n">
-        <v>247</v>
+        <v>314</v>
       </c>
       <c r="I25" t="n">
-        <v>11405</v>
+        <v>12168</v>
       </c>
       <c r="J25" t="n">
-        <v>14729</v>
+        <v>16926</v>
       </c>
       <c r="K25" t="n">
-        <v>0.022</v>
+        <v>0.0204</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2424</v>
+        <v>0.2589</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2528</v>
+        <v>0.2713</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>202405</v>
+        <v>202407</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20240501</t>
+          <t>20240701</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2191</v>
+        <v>1998</v>
       </c>
       <c r="D26" t="n">
-        <v>9393</v>
+        <v>13178</v>
       </c>
       <c r="E26" t="n">
-        <v>32883</v>
+        <v>36644</v>
       </c>
       <c r="F26" t="n">
-        <v>47048</v>
+        <v>47004</v>
       </c>
       <c r="G26" t="n">
-        <v>56441</v>
+        <v>60182</v>
       </c>
       <c r="H26" t="n">
-        <v>369</v>
+        <v>286</v>
       </c>
       <c r="I26" t="n">
-        <v>10947</v>
+        <v>11803</v>
       </c>
       <c r="J26" t="n">
-        <v>13671</v>
+        <v>15825</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0393</v>
+        <v>0.0217</v>
       </c>
       <c r="L26" t="n">
-        <v>0.2327</v>
+        <v>0.2511</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2422</v>
+        <v>0.263</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>202404</v>
+        <v>202406</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20240401</t>
+          <t>20240601</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2222</v>
+        <v>1808</v>
       </c>
       <c r="D27" t="n">
-        <v>7202</v>
+        <v>11180</v>
       </c>
       <c r="E27" t="n">
-        <v>30692</v>
+        <v>34646</v>
       </c>
       <c r="F27" t="n">
-        <v>47048</v>
+        <v>47004</v>
       </c>
       <c r="G27" t="n">
-        <v>54250</v>
+        <v>58184</v>
       </c>
       <c r="H27" t="n">
-        <v>376</v>
+        <v>246</v>
       </c>
       <c r="I27" t="n">
-        <v>10407</v>
+        <v>11389</v>
       </c>
       <c r="J27" t="n">
-        <v>12366</v>
+        <v>14703</v>
       </c>
       <c r="K27" t="n">
-        <v>0.0522</v>
+        <v>0.022</v>
       </c>
       <c r="L27" t="n">
-        <v>0.2212</v>
+        <v>0.2423</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2279</v>
+        <v>0.2527</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>202403</v>
+        <v>202405</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20240301</t>
+          <t>20240501</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1808</v>
+        <v>2185</v>
       </c>
       <c r="D28" t="n">
-        <v>4980</v>
+        <v>9372</v>
       </c>
       <c r="E28" t="n">
-        <v>28470</v>
+        <v>32838</v>
       </c>
       <c r="F28" t="n">
-        <v>47048</v>
+        <v>47004</v>
       </c>
       <c r="G28" t="n">
-        <v>52028</v>
+        <v>56376</v>
       </c>
       <c r="H28" t="n">
-        <v>288</v>
+        <v>367</v>
       </c>
       <c r="I28" t="n">
-        <v>9689</v>
+        <v>10931</v>
       </c>
       <c r="J28" t="n">
-        <v>10954</v>
+        <v>13647</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0578</v>
+        <v>0.0392</v>
       </c>
       <c r="L28" t="n">
-        <v>0.2059</v>
+        <v>0.2326</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2105</v>
+        <v>0.2421</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>202402</v>
+        <v>202404</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20240201</t>
+          <t>20240401</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1855</v>
+        <v>2218</v>
       </c>
       <c r="D29" t="n">
-        <v>3172</v>
+        <v>7187</v>
       </c>
       <c r="E29" t="n">
-        <v>26662</v>
+        <v>30653</v>
       </c>
       <c r="F29" t="n">
-        <v>47048</v>
+        <v>47004</v>
       </c>
       <c r="G29" t="n">
-        <v>50220</v>
+        <v>54191</v>
       </c>
       <c r="H29" t="n">
-        <v>345</v>
+        <v>375</v>
       </c>
       <c r="I29" t="n">
-        <v>8726</v>
+        <v>10391</v>
       </c>
       <c r="J29" t="n">
-        <v>9439</v>
+        <v>12346</v>
       </c>
       <c r="K29" t="n">
-        <v>0.1088</v>
+        <v>0.0522</v>
       </c>
       <c r="L29" t="n">
-        <v>0.1855</v>
+        <v>0.2211</v>
       </c>
       <c r="M29" t="n">
-        <v>0.188</v>
+        <v>0.2278</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>202401</v>
+        <v>202403</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20240101</t>
+          <t>20240301</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1317</v>
+        <v>1804</v>
       </c>
       <c r="D30" t="n">
-        <v>1317</v>
+        <v>4969</v>
       </c>
       <c r="E30" t="n">
-        <v>24807</v>
+        <v>28435</v>
       </c>
       <c r="F30" t="n">
-        <v>47048</v>
+        <v>47004</v>
       </c>
       <c r="G30" t="n">
-        <v>48365</v>
+        <v>51973</v>
       </c>
       <c r="H30" t="n">
-        <v>206</v>
+        <v>287</v>
       </c>
       <c r="I30" t="n">
-        <v>7155</v>
+        <v>9674</v>
       </c>
       <c r="J30" t="n">
-        <v>7361</v>
+        <v>10937</v>
       </c>
       <c r="K30" t="n">
-        <v>0.1564</v>
+        <v>0.0578</v>
       </c>
       <c r="L30" t="n">
-        <v>0.1521</v>
+        <v>0.2058</v>
       </c>
       <c r="M30" t="n">
-        <v>0.1522</v>
+        <v>0.2104</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>202312</v>
+        <v>202402</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20231201</t>
+          <t>20240201</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1283</v>
+        <v>1853</v>
       </c>
       <c r="D31" t="n">
-        <v>13233</v>
+        <v>3165</v>
       </c>
       <c r="E31" t="n">
-        <v>23490</v>
+        <v>26631</v>
       </c>
       <c r="F31" t="n">
-        <v>33815</v>
+        <v>47004</v>
       </c>
       <c r="G31" t="n">
-        <v>47048</v>
+        <v>50169</v>
       </c>
       <c r="H31" t="n">
-        <v>171</v>
+        <v>345</v>
       </c>
       <c r="I31" t="n">
-        <v>10318</v>
+        <v>8711</v>
       </c>
       <c r="J31" t="n">
-        <v>15991</v>
+        <v>9423</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0129</v>
+        <v>0.109</v>
       </c>
       <c r="L31" t="n">
-        <v>0.3051</v>
+        <v>0.1853</v>
       </c>
       <c r="M31" t="n">
-        <v>0.3399</v>
+        <v>0.1878</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>202311</v>
+        <v>202401</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20231101</t>
+          <t>20240101</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1419</v>
+        <v>1312</v>
       </c>
       <c r="D32" t="n">
-        <v>11950</v>
+        <v>1312</v>
       </c>
       <c r="E32" t="n">
-        <v>22207</v>
+        <v>24778</v>
       </c>
       <c r="F32" t="n">
-        <v>33815</v>
+        <v>47004</v>
       </c>
       <c r="G32" t="n">
-        <v>45765</v>
+        <v>48316</v>
       </c>
       <c r="H32" t="n">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="I32" t="n">
-        <v>10165</v>
+        <v>7145</v>
       </c>
       <c r="J32" t="n">
-        <v>15288</v>
+        <v>7350</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0187</v>
+        <v>0.1563</v>
       </c>
       <c r="L32" t="n">
-        <v>0.3006</v>
+        <v>0.152</v>
       </c>
       <c r="M32" t="n">
-        <v>0.3341</v>
+        <v>0.1521</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>202310</v>
+        <v>202312</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20231001</t>
+          <t>20231201</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1369</v>
+        <v>1283</v>
       </c>
       <c r="D33" t="n">
-        <v>10531</v>
+        <v>13224</v>
       </c>
       <c r="E33" t="n">
-        <v>20788</v>
+        <v>23466</v>
       </c>
       <c r="F33" t="n">
-        <v>33815</v>
+        <v>33780</v>
       </c>
       <c r="G33" t="n">
-        <v>44346</v>
+        <v>47004</v>
       </c>
       <c r="H33" t="n">
-        <v>204</v>
+        <v>171</v>
       </c>
       <c r="I33" t="n">
-        <v>9977</v>
+        <v>10305</v>
       </c>
       <c r="J33" t="n">
-        <v>14488</v>
+        <v>15974</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0194</v>
+        <v>0.0129</v>
       </c>
       <c r="L33" t="n">
-        <v>0.295</v>
+        <v>0.3051</v>
       </c>
       <c r="M33" t="n">
-        <v>0.3267</v>
+        <v>0.3398</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>202309</v>
+        <v>202311</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20230901</t>
+          <t>20231101</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1353</v>
+        <v>1419</v>
       </c>
       <c r="D34" t="n">
-        <v>9162</v>
+        <v>11941</v>
       </c>
       <c r="E34" t="n">
-        <v>19419</v>
+        <v>22183</v>
       </c>
       <c r="F34" t="n">
-        <v>33815</v>
+        <v>33780</v>
       </c>
       <c r="G34" t="n">
-        <v>42977</v>
+        <v>45721</v>
       </c>
       <c r="H34" t="n">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="I34" t="n">
-        <v>9742</v>
+        <v>10153</v>
       </c>
       <c r="J34" t="n">
-        <v>13692</v>
+        <v>15272</v>
       </c>
       <c r="K34" t="n">
-        <v>0.0266</v>
+        <v>0.0188</v>
       </c>
       <c r="L34" t="n">
-        <v>0.2881</v>
+        <v>0.3006</v>
       </c>
       <c r="M34" t="n">
-        <v>0.3186</v>
+        <v>0.334</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>202308</v>
+        <v>202310</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20230801</t>
+          <t>20231001</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1073</v>
+        <v>1370</v>
       </c>
       <c r="D35" t="n">
-        <v>7809</v>
+        <v>10522</v>
       </c>
       <c r="E35" t="n">
-        <v>18066</v>
+        <v>20764</v>
       </c>
       <c r="F35" t="n">
-        <v>33815</v>
+        <v>33780</v>
       </c>
       <c r="G35" t="n">
-        <v>41624</v>
+        <v>44302</v>
       </c>
       <c r="H35" t="n">
-        <v>243</v>
+        <v>204</v>
       </c>
       <c r="I35" t="n">
-        <v>9521</v>
+        <v>9964</v>
       </c>
       <c r="J35" t="n">
-        <v>12893</v>
+        <v>14471</v>
       </c>
       <c r="K35" t="n">
-        <v>0.0311</v>
+        <v>0.0194</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2816</v>
+        <v>0.295</v>
       </c>
       <c r="M35" t="n">
-        <v>0.3097</v>
+        <v>0.3266</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>202307</v>
+        <v>202309</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20230701</t>
+          <t>20230901</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>943</v>
+        <v>1352</v>
       </c>
       <c r="D36" t="n">
-        <v>6736</v>
+        <v>9152</v>
       </c>
       <c r="E36" t="n">
-        <v>16993</v>
+        <v>19394</v>
       </c>
       <c r="F36" t="n">
-        <v>33815</v>
+        <v>33780</v>
       </c>
       <c r="G36" t="n">
-        <v>40551</v>
+        <v>42932</v>
       </c>
       <c r="H36" t="n">
-        <v>191</v>
+        <v>244</v>
       </c>
       <c r="I36" t="n">
-        <v>9211</v>
+        <v>9730</v>
       </c>
       <c r="J36" t="n">
-        <v>11997</v>
+        <v>13676</v>
       </c>
       <c r="K36" t="n">
-        <v>0.0284</v>
+        <v>0.0267</v>
       </c>
       <c r="L36" t="n">
-        <v>0.2724</v>
+        <v>0.288</v>
       </c>
       <c r="M36" t="n">
-        <v>0.2958</v>
+        <v>0.3186</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>202306</v>
+        <v>202308</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20230601</t>
+          <t>20230801</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>997</v>
+        <v>1071</v>
       </c>
       <c r="D37" t="n">
-        <v>5793</v>
+        <v>7800</v>
       </c>
       <c r="E37" t="n">
-        <v>16050</v>
+        <v>18042</v>
       </c>
       <c r="F37" t="n">
-        <v>33815</v>
+        <v>33780</v>
       </c>
       <c r="G37" t="n">
-        <v>39608</v>
+        <v>41580</v>
       </c>
       <c r="H37" t="n">
-        <v>210</v>
+        <v>242</v>
       </c>
       <c r="I37" t="n">
-        <v>8908</v>
+        <v>9509</v>
       </c>
       <c r="J37" t="n">
-        <v>11206</v>
+        <v>12877</v>
       </c>
       <c r="K37" t="n">
-        <v>0.0363</v>
+        <v>0.031</v>
       </c>
       <c r="L37" t="n">
-        <v>0.2634</v>
+        <v>0.2815</v>
       </c>
       <c r="M37" t="n">
-        <v>0.2829</v>
+        <v>0.3097</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>202305</v>
+        <v>202307</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20230501</t>
+          <t>20230701</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>931</v>
+        <v>943</v>
       </c>
       <c r="D38" t="n">
-        <v>4796</v>
+        <v>6729</v>
       </c>
       <c r="E38" t="n">
-        <v>15053</v>
+        <v>16971</v>
       </c>
       <c r="F38" t="n">
-        <v>33815</v>
+        <v>33780</v>
       </c>
       <c r="G38" t="n">
-        <v>38611</v>
+        <v>40509</v>
       </c>
       <c r="H38" t="n">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="I38" t="n">
-        <v>8563</v>
+        <v>9199</v>
       </c>
       <c r="J38" t="n">
-        <v>10392</v>
+        <v>11983</v>
       </c>
       <c r="K38" t="n">
-        <v>0.0409</v>
+        <v>0.0284</v>
       </c>
       <c r="L38" t="n">
-        <v>0.2532</v>
+        <v>0.2723</v>
       </c>
       <c r="M38" t="n">
-        <v>0.2691</v>
+        <v>0.2958</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>202304</v>
+        <v>202306</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20230401</t>
+          <t>20230601</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>908</v>
+        <v>997</v>
       </c>
       <c r="D39" t="n">
-        <v>3865</v>
+        <v>5786</v>
       </c>
       <c r="E39" t="n">
-        <v>14122</v>
+        <v>16028</v>
       </c>
       <c r="F39" t="n">
-        <v>33815</v>
+        <v>33780</v>
       </c>
       <c r="G39" t="n">
-        <v>37680</v>
+        <v>39566</v>
       </c>
       <c r="H39" t="n">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="I39" t="n">
-        <v>8115</v>
+        <v>8898</v>
       </c>
       <c r="J39" t="n">
-        <v>9517</v>
+        <v>11195</v>
       </c>
       <c r="K39" t="n">
-        <v>0.0528</v>
+        <v>0.0363</v>
       </c>
       <c r="L39" t="n">
-        <v>0.24</v>
+        <v>0.2634</v>
       </c>
       <c r="M39" t="n">
-        <v>0.2526</v>
+        <v>0.2829</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>202303</v>
+        <v>202305</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20230301</t>
+          <t>20230501</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1084</v>
+        <v>925</v>
       </c>
       <c r="D40" t="n">
-        <v>2957</v>
+        <v>4789</v>
       </c>
       <c r="E40" t="n">
-        <v>13214</v>
+        <v>15031</v>
       </c>
       <c r="F40" t="n">
-        <v>33815</v>
+        <v>33780</v>
       </c>
       <c r="G40" t="n">
-        <v>36772</v>
+        <v>38569</v>
       </c>
       <c r="H40" t="n">
-        <v>220</v>
+        <v>195</v>
       </c>
       <c r="I40" t="n">
-        <v>7580</v>
+        <v>8553</v>
       </c>
       <c r="J40" t="n">
-        <v>8544</v>
+        <v>10381</v>
       </c>
       <c r="K40" t="n">
-        <v>0.07439999999999999</v>
+        <v>0.0407</v>
       </c>
       <c r="L40" t="n">
-        <v>0.2242</v>
+        <v>0.2532</v>
       </c>
       <c r="M40" t="n">
-        <v>0.2324</v>
+        <v>0.2692</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>202302</v>
+        <v>202304</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20230201</t>
+          <t>20230401</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>972</v>
+        <v>908</v>
       </c>
       <c r="D41" t="n">
-        <v>1873</v>
+        <v>3864</v>
       </c>
       <c r="E41" t="n">
-        <v>12130</v>
+        <v>14106</v>
       </c>
       <c r="F41" t="n">
-        <v>33815</v>
+        <v>33780</v>
       </c>
       <c r="G41" t="n">
-        <v>35688</v>
+        <v>37644</v>
       </c>
       <c r="H41" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I41" t="n">
-        <v>6729</v>
+        <v>8105</v>
       </c>
       <c r="J41" t="n">
-        <v>7274</v>
+        <v>9507</v>
       </c>
       <c r="K41" t="n">
-        <v>0.11</v>
+        <v>0.0531</v>
       </c>
       <c r="L41" t="n">
-        <v>0.199</v>
+        <v>0.2399</v>
       </c>
       <c r="M41" t="n">
-        <v>0.2038</v>
+        <v>0.2526</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>202301</v>
+        <v>202303</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>20230101</t>
+          <t>20230301</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>901</v>
+        <v>1082</v>
       </c>
       <c r="D42" t="n">
-        <v>901</v>
+        <v>2956</v>
       </c>
       <c r="E42" t="n">
-        <v>11158</v>
+        <v>13198</v>
       </c>
       <c r="F42" t="n">
-        <v>33815</v>
+        <v>33780</v>
       </c>
       <c r="G42" t="n">
-        <v>34716</v>
+        <v>36736</v>
       </c>
       <c r="H42" t="n">
-        <v>188</v>
+        <v>220</v>
       </c>
       <c r="I42" t="n">
-        <v>5497</v>
+        <v>7570</v>
       </c>
       <c r="J42" t="n">
-        <v>5685</v>
+        <v>8534</v>
       </c>
       <c r="K42" t="n">
-        <v>0.2087</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>0.1626</v>
+        <v>0.2241</v>
       </c>
       <c r="M42" t="n">
-        <v>0.1638</v>
+        <v>0.2323</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>202212</v>
+        <v>202302</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>20221201</t>
+          <t>20230201</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>692</v>
+        <v>973</v>
       </c>
       <c r="D43" t="n">
-        <v>10257</v>
+        <v>1874</v>
       </c>
       <c r="E43" t="n">
-        <v>10257</v>
+        <v>12116</v>
       </c>
       <c r="F43" t="n">
-        <v>23558</v>
+        <v>33780</v>
       </c>
       <c r="G43" t="n">
-        <v>33815</v>
+        <v>35654</v>
       </c>
       <c r="H43" t="n">
-        <v>135</v>
+        <v>206</v>
       </c>
       <c r="I43" t="n">
-        <v>8041</v>
+        <v>6720</v>
       </c>
       <c r="J43" t="n">
-        <v>12366</v>
+        <v>7265</v>
       </c>
       <c r="K43" t="n">
-        <v>0.0132</v>
+        <v>0.1099</v>
       </c>
       <c r="L43" t="n">
-        <v>0.3413</v>
+        <v>0.1989</v>
       </c>
       <c r="M43" t="n">
-        <v>0.3657</v>
+        <v>0.2038</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>202211</v>
+        <v>202301</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>20221101</t>
+          <t>20230101</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1040</v>
+        <v>901</v>
       </c>
       <c r="D44" t="n">
-        <v>9565</v>
+        <v>901</v>
       </c>
       <c r="E44" t="n">
-        <v>9565</v>
+        <v>11143</v>
       </c>
       <c r="F44" t="n">
-        <v>23558</v>
+        <v>33780</v>
       </c>
       <c r="G44" t="n">
-        <v>33123</v>
+        <v>34681</v>
       </c>
       <c r="H44" t="n">
-        <v>215</v>
+        <v>188</v>
       </c>
       <c r="I44" t="n">
-        <v>7908</v>
+        <v>5489</v>
       </c>
       <c r="J44" t="n">
-        <v>11833</v>
+        <v>5677</v>
       </c>
       <c r="K44" t="n">
-        <v>0.0225</v>
+        <v>0.2087</v>
       </c>
       <c r="L44" t="n">
-        <v>0.3357</v>
+        <v>0.1625</v>
       </c>
       <c r="M44" t="n">
-        <v>0.3572</v>
+        <v>0.1637</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>202210</v>
+        <v>202212</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20221001</t>
+          <t>20221201</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>962</v>
+        <v>691</v>
       </c>
       <c r="D45" t="n">
-        <v>8525</v>
+        <v>10242</v>
       </c>
       <c r="E45" t="n">
-        <v>8525</v>
+        <v>10242</v>
       </c>
       <c r="F45" t="n">
-        <v>23558</v>
+        <v>23538</v>
       </c>
       <c r="G45" t="n">
-        <v>32083</v>
+        <v>33780</v>
       </c>
       <c r="H45" t="n">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="I45" t="n">
-        <v>7741</v>
+        <v>8031</v>
       </c>
       <c r="J45" t="n">
-        <v>11135</v>
+        <v>12349</v>
       </c>
       <c r="K45" t="n">
-        <v>0.0211</v>
+        <v>0.0132</v>
       </c>
       <c r="L45" t="n">
-        <v>0.3286</v>
+        <v>0.3412</v>
       </c>
       <c r="M45" t="n">
-        <v>0.3471</v>
+        <v>0.3656</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>202209</v>
+        <v>202211</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>20220901</t>
+          <t>20221101</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1029</v>
+        <v>1040</v>
       </c>
       <c r="D46" t="n">
-        <v>7563</v>
+        <v>9551</v>
       </c>
       <c r="E46" t="n">
-        <v>7563</v>
+        <v>9551</v>
       </c>
       <c r="F46" t="n">
-        <v>23558</v>
+        <v>23538</v>
       </c>
       <c r="G46" t="n">
-        <v>31121</v>
+        <v>33089</v>
       </c>
       <c r="H46" t="n">
-        <v>187</v>
+        <v>215</v>
       </c>
       <c r="I46" t="n">
-        <v>7569</v>
+        <v>7899</v>
       </c>
       <c r="J46" t="n">
-        <v>10535</v>
+        <v>11818</v>
       </c>
       <c r="K46" t="n">
-        <v>0.0247</v>
+        <v>0.0225</v>
       </c>
       <c r="L46" t="n">
-        <v>0.3213</v>
+        <v>0.3356</v>
       </c>
       <c r="M46" t="n">
-        <v>0.3385</v>
+        <v>0.3572</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>202208</v>
+        <v>202210</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>20220801</t>
+          <t>20221001</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1050</v>
+        <v>961</v>
       </c>
       <c r="D47" t="n">
-        <v>6534</v>
+        <v>8511</v>
       </c>
       <c r="E47" t="n">
-        <v>6534</v>
+        <v>8511</v>
       </c>
       <c r="F47" t="n">
-        <v>23558</v>
+        <v>23538</v>
       </c>
       <c r="G47" t="n">
-        <v>30092</v>
+        <v>32049</v>
       </c>
       <c r="H47" t="n">
-        <v>211</v>
+        <v>180</v>
       </c>
       <c r="I47" t="n">
-        <v>7374</v>
+        <v>7732</v>
       </c>
       <c r="J47" t="n">
-        <v>9913</v>
+        <v>11120</v>
       </c>
       <c r="K47" t="n">
-        <v>0.0323</v>
+        <v>0.0211</v>
       </c>
       <c r="L47" t="n">
-        <v>0.313</v>
+        <v>0.3285</v>
       </c>
       <c r="M47" t="n">
-        <v>0.3294</v>
+        <v>0.347</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>202207</v>
+        <v>202209</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20220701</t>
+          <t>20220901</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>807</v>
+        <v>1027</v>
       </c>
       <c r="D48" t="n">
-        <v>5484</v>
+        <v>7550</v>
       </c>
       <c r="E48" t="n">
-        <v>5484</v>
+        <v>7550</v>
       </c>
       <c r="F48" t="n">
-        <v>23558</v>
+        <v>23538</v>
       </c>
       <c r="G48" t="n">
-        <v>29042</v>
+        <v>31088</v>
       </c>
       <c r="H48" t="n">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="I48" t="n">
-        <v>7149</v>
+        <v>7561</v>
       </c>
       <c r="J48" t="n">
-        <v>9273</v>
+        <v>10521</v>
       </c>
       <c r="K48" t="n">
-        <v>0.0301</v>
+        <v>0.0246</v>
       </c>
       <c r="L48" t="n">
-        <v>0.3035</v>
+        <v>0.3212</v>
       </c>
       <c r="M48" t="n">
-        <v>0.3193</v>
+        <v>0.3384</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>202206</v>
+        <v>202208</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20220601</t>
+          <t>20220801</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>793</v>
+        <v>1048</v>
       </c>
       <c r="D49" t="n">
-        <v>4677</v>
+        <v>6523</v>
       </c>
       <c r="E49" t="n">
-        <v>4677</v>
+        <v>6523</v>
       </c>
       <c r="F49" t="n">
-        <v>23558</v>
+        <v>23538</v>
       </c>
       <c r="G49" t="n">
-        <v>28235</v>
+        <v>30061</v>
       </c>
       <c r="H49" t="n">
-        <v>178</v>
+        <v>211</v>
       </c>
       <c r="I49" t="n">
-        <v>6924</v>
+        <v>7365</v>
       </c>
       <c r="J49" t="n">
-        <v>8701</v>
+        <v>9899</v>
       </c>
       <c r="K49" t="n">
-        <v>0.0381</v>
+        <v>0.0323</v>
       </c>
       <c r="L49" t="n">
-        <v>0.2939</v>
+        <v>0.3129</v>
       </c>
       <c r="M49" t="n">
-        <v>0.3082</v>
+        <v>0.3293</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>202205</v>
+        <v>202207</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>20220501</t>
+          <t>20220701</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>821</v>
+        <v>807</v>
       </c>
       <c r="D50" t="n">
-        <v>3884</v>
+        <v>5475</v>
       </c>
       <c r="E50" t="n">
-        <v>3884</v>
+        <v>5475</v>
       </c>
       <c r="F50" t="n">
-        <v>23558</v>
+        <v>23538</v>
       </c>
       <c r="G50" t="n">
-        <v>27442</v>
+        <v>29013</v>
       </c>
       <c r="H50" t="n">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="I50" t="n">
-        <v>6622</v>
+        <v>7140</v>
       </c>
       <c r="J50" t="n">
-        <v>8027</v>
+        <v>9260</v>
       </c>
       <c r="K50" t="n">
-        <v>0.0456</v>
+        <v>0.0301</v>
       </c>
       <c r="L50" t="n">
-        <v>0.2811</v>
+        <v>0.3033</v>
       </c>
       <c r="M50" t="n">
-        <v>0.2925</v>
+        <v>0.3192</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>202204</v>
+        <v>202206</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>20220401</t>
+          <t>20220601</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>749</v>
+        <v>792</v>
       </c>
       <c r="D51" t="n">
-        <v>3063</v>
+        <v>4668</v>
       </c>
       <c r="E51" t="n">
-        <v>3063</v>
+        <v>4668</v>
       </c>
       <c r="F51" t="n">
-        <v>23558</v>
+        <v>23538</v>
       </c>
       <c r="G51" t="n">
-        <v>26621</v>
+        <v>28206</v>
       </c>
       <c r="H51" t="n">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="I51" t="n">
-        <v>6248</v>
+        <v>6915</v>
       </c>
       <c r="J51" t="n">
-        <v>7309</v>
+        <v>8689</v>
       </c>
       <c r="K51" t="n">
-        <v>0.0506</v>
+        <v>0.0381</v>
       </c>
       <c r="L51" t="n">
-        <v>0.2652</v>
+        <v>0.2938</v>
       </c>
       <c r="M51" t="n">
-        <v>0.2746</v>
+        <v>0.3081</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>202203</v>
+        <v>202205</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20220301</t>
+          <t>20220501</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>945</v>
+        <v>820</v>
       </c>
       <c r="D52" t="n">
-        <v>2314</v>
+        <v>3876</v>
       </c>
       <c r="E52" t="n">
-        <v>2314</v>
+        <v>3876</v>
       </c>
       <c r="F52" t="n">
-        <v>23558</v>
+        <v>23538</v>
       </c>
       <c r="G52" t="n">
-        <v>25872</v>
+        <v>27414</v>
       </c>
       <c r="H52" t="n">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="I52" t="n">
-        <v>5830</v>
+        <v>6614</v>
       </c>
       <c r="J52" t="n">
-        <v>6592</v>
+        <v>8016</v>
       </c>
       <c r="K52" t="n">
-        <v>0.0834</v>
+        <v>0.0454</v>
       </c>
       <c r="L52" t="n">
-        <v>0.2475</v>
+        <v>0.281</v>
       </c>
       <c r="M52" t="n">
-        <v>0.2548</v>
+        <v>0.2924</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>202202</v>
+        <v>202204</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>20220201</t>
+          <t>20220401</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="D53" t="n">
-        <v>1369</v>
+        <v>3056</v>
       </c>
       <c r="E53" t="n">
-        <v>1369</v>
+        <v>3056</v>
       </c>
       <c r="F53" t="n">
-        <v>23558</v>
+        <v>23538</v>
       </c>
       <c r="G53" t="n">
-        <v>24927</v>
+        <v>26594</v>
       </c>
       <c r="H53" t="n">
-        <v>182</v>
+        <v>154</v>
       </c>
       <c r="I53" t="n">
-        <v>5154</v>
+        <v>6240</v>
       </c>
       <c r="J53" t="n">
-        <v>5569</v>
+        <v>7300</v>
       </c>
       <c r="K53" t="n">
-        <v>0.1329</v>
+        <v>0.0504</v>
       </c>
       <c r="L53" t="n">
-        <v>0.2188</v>
+        <v>0.2651</v>
       </c>
       <c r="M53" t="n">
-        <v>0.2234</v>
+        <v>0.2745</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
+        <v>202203</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>20220301</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>943</v>
+      </c>
+      <c r="D54" t="n">
+        <v>2310</v>
+      </c>
+      <c r="E54" t="n">
+        <v>2310</v>
+      </c>
+      <c r="F54" t="n">
+        <v>23538</v>
+      </c>
+      <c r="G54" t="n">
+        <v>25848</v>
+      </c>
+      <c r="H54" t="n">
+        <v>193</v>
+      </c>
+      <c r="I54" t="n">
+        <v>5823</v>
+      </c>
+      <c r="J54" t="n">
+        <v>6585</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.0835</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.2474</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.2548</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>202202</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>20220201</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>739</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1367</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1367</v>
+      </c>
+      <c r="F55" t="n">
+        <v>23538</v>
+      </c>
+      <c r="G55" t="n">
+        <v>24905</v>
+      </c>
+      <c r="H55" t="n">
+        <v>182</v>
+      </c>
+      <c r="I55" t="n">
+        <v>5146</v>
+      </c>
+      <c r="J55" t="n">
+        <v>5561</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.1331</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.2186</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.2233</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
         <v>202201</v>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>20220101</t>
         </is>
       </c>
-      <c r="C54" t="n">
-        <v>629</v>
-      </c>
-      <c r="D54" t="n">
-        <v>629</v>
-      </c>
-      <c r="E54" t="n">
-        <v>629</v>
-      </c>
-      <c r="F54" t="n">
-        <v>23558</v>
-      </c>
-      <c r="G54" t="n">
-        <v>24187</v>
-      </c>
-      <c r="H54" t="n">
+      <c r="C56" t="n">
+        <v>628</v>
+      </c>
+      <c r="D56" t="n">
+        <v>628</v>
+      </c>
+      <c r="E56" t="n">
+        <v>628</v>
+      </c>
+      <c r="F56" t="n">
+        <v>23538</v>
+      </c>
+      <c r="G56" t="n">
+        <v>24166</v>
+      </c>
+      <c r="H56" t="n">
         <v>145</v>
       </c>
-      <c r="I54" t="n">
-        <v>4174</v>
-      </c>
-      <c r="J54" t="n">
-        <v>4319</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0.2305</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0.1772</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0.1786</v>
+      <c r="I56" t="n">
+        <v>4167</v>
+      </c>
+      <c r="J56" t="n">
+        <v>4312</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.2309</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.1784</v>
       </c>
     </row>
   </sheetData>

--- a/main_data/evolucion_vinculacion_y_uso_wompi_vinc_primer_regi.xlsx
+++ b/main_data/evolucion_vinculacion_y_uso_wompi_vinc_primer_regi.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M56"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,2366 +497,2409 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>202607</v>
+        <v>202608</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260801</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7839</v>
+        <v>23831</v>
       </c>
       <c r="D2" t="n">
-        <v>47146</v>
+        <v>70977</v>
       </c>
       <c r="E2" t="n">
-        <v>135772</v>
+        <v>159603</v>
       </c>
       <c r="F2" t="n">
-        <v>112164</v>
+        <v>144948</v>
       </c>
       <c r="G2" t="n">
-        <v>159310</v>
+        <v>289803</v>
       </c>
       <c r="H2" t="n">
-        <v>1645</v>
+        <v>2979</v>
       </c>
       <c r="I2" t="n">
-        <v>21208</v>
+        <v>25926</v>
       </c>
       <c r="J2" t="n">
-        <v>34124</v>
+        <v>53868</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0349</v>
+        <v>0.042</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1891</v>
+        <v>0.1789</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2142</v>
+        <v>0.1859</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>202606</v>
+        <v>202607</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6988</v>
+        <v>7839</v>
       </c>
       <c r="D3" t="n">
-        <v>39307</v>
+        <v>47146</v>
       </c>
       <c r="E3" t="n">
-        <v>127933</v>
+        <v>135772</v>
       </c>
       <c r="F3" t="n">
         <v>112164</v>
       </c>
       <c r="G3" t="n">
-        <v>151471</v>
+        <v>159310</v>
       </c>
       <c r="H3" t="n">
-        <v>1128</v>
+        <v>1645</v>
       </c>
       <c r="I3" t="n">
-        <v>20297</v>
+        <v>21208</v>
       </c>
       <c r="J3" t="n">
-        <v>30139</v>
+        <v>34124</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0287</v>
+        <v>0.0349</v>
       </c>
       <c r="L3" t="n">
-        <v>0.181</v>
+        <v>0.1891</v>
       </c>
       <c r="M3" t="n">
-        <v>0.199</v>
+        <v>0.2142</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>202605</v>
+        <v>202606</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7204</v>
+        <v>6988</v>
       </c>
       <c r="D4" t="n">
-        <v>32319</v>
+        <v>39307</v>
       </c>
       <c r="E4" t="n">
-        <v>120945</v>
+        <v>127933</v>
       </c>
       <c r="F4" t="n">
         <v>112164</v>
       </c>
       <c r="G4" t="n">
-        <v>144483</v>
+        <v>151471</v>
       </c>
       <c r="H4" t="n">
-        <v>1200</v>
+        <v>1128</v>
       </c>
       <c r="I4" t="n">
-        <v>19366</v>
+        <v>20297</v>
       </c>
       <c r="J4" t="n">
-        <v>26945</v>
+        <v>30139</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0371</v>
+        <v>0.0287</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1727</v>
+        <v>0.181</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1865</v>
+        <v>0.199</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>202604</v>
+        <v>202605</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20260401</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7681</v>
+        <v>7204</v>
       </c>
       <c r="D5" t="n">
-        <v>25115</v>
+        <v>32319</v>
       </c>
       <c r="E5" t="n">
-        <v>113741</v>
+        <v>120945</v>
       </c>
       <c r="F5" t="n">
         <v>112164</v>
       </c>
       <c r="G5" t="n">
-        <v>137279</v>
+        <v>144483</v>
       </c>
       <c r="H5" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="I5" t="n">
-        <v>18226</v>
+        <v>19366</v>
       </c>
       <c r="J5" t="n">
-        <v>23516</v>
+        <v>26945</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0438</v>
+        <v>0.0371</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1625</v>
+        <v>0.1727</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1713</v>
+        <v>0.1865</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>202603</v>
+        <v>202604</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20260301</t>
+          <t>20260401</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7054</v>
+        <v>7681</v>
       </c>
       <c r="D6" t="n">
-        <v>17434</v>
+        <v>25115</v>
       </c>
       <c r="E6" t="n">
-        <v>106060</v>
+        <v>113741</v>
       </c>
       <c r="F6" t="n">
         <v>112164</v>
       </c>
       <c r="G6" t="n">
-        <v>129598</v>
+        <v>137279</v>
       </c>
       <c r="H6" t="n">
-        <v>959</v>
+        <v>1100</v>
       </c>
       <c r="I6" t="n">
-        <v>16906</v>
+        <v>18226</v>
       </c>
       <c r="J6" t="n">
-        <v>20119</v>
+        <v>23516</v>
       </c>
       <c r="K6" t="n">
-        <v>0.055</v>
+        <v>0.0438</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1507</v>
+        <v>0.1625</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1552</v>
+        <v>0.1713</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>202602</v>
+        <v>202603</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20260201</t>
+          <t>20260301</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5684</v>
+        <v>7054</v>
       </c>
       <c r="D7" t="n">
-        <v>10380</v>
+        <v>17434</v>
       </c>
       <c r="E7" t="n">
-        <v>99006</v>
+        <v>106060</v>
       </c>
       <c r="F7" t="n">
         <v>112164</v>
       </c>
       <c r="G7" t="n">
-        <v>122544</v>
+        <v>129598</v>
       </c>
       <c r="H7" t="n">
-        <v>714</v>
+        <v>959</v>
       </c>
       <c r="I7" t="n">
-        <v>15002</v>
+        <v>16906</v>
       </c>
       <c r="J7" t="n">
-        <v>16662</v>
+        <v>20119</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0688</v>
+        <v>0.055</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1338</v>
+        <v>0.1507</v>
       </c>
       <c r="M7" t="n">
-        <v>0.136</v>
+        <v>0.1552</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>202601</v>
+        <v>202602</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20260101</t>
+          <t>20260201</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4696</v>
+        <v>5684</v>
       </c>
       <c r="D8" t="n">
-        <v>4696</v>
+        <v>10380</v>
       </c>
       <c r="E8" t="n">
-        <v>93322</v>
+        <v>99006</v>
       </c>
       <c r="F8" t="n">
         <v>112164</v>
       </c>
       <c r="G8" t="n">
-        <v>116860</v>
+        <v>122544</v>
       </c>
       <c r="H8" t="n">
-        <v>565</v>
+        <v>714</v>
       </c>
       <c r="I8" t="n">
-        <v>12252</v>
+        <v>15002</v>
       </c>
       <c r="J8" t="n">
-        <v>12817</v>
+        <v>16662</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1203</v>
+        <v>0.0688</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1092</v>
+        <v>0.1338</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1097</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20251201</t>
+          <t>20260101</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4244</v>
+        <v>4696</v>
       </c>
       <c r="D9" t="n">
-        <v>40753</v>
+        <v>4696</v>
       </c>
       <c r="E9" t="n">
-        <v>88626</v>
+        <v>93322</v>
       </c>
       <c r="F9" t="n">
-        <v>71411</v>
+        <v>112164</v>
       </c>
       <c r="G9" t="n">
-        <v>112164</v>
+        <v>116860</v>
       </c>
       <c r="H9" t="n">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c r="I9" t="n">
-        <v>17336</v>
+        <v>12252</v>
       </c>
       <c r="J9" t="n">
-        <v>28149</v>
+        <v>12817</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0136</v>
+        <v>0.1203</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2428</v>
+        <v>0.1092</v>
       </c>
       <c r="M9" t="n">
-        <v>0.251</v>
+        <v>0.1097</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>202511</v>
+        <v>202512</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20251101</t>
+          <t>20251201</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4653</v>
+        <v>4244</v>
       </c>
       <c r="D10" t="n">
-        <v>36509</v>
+        <v>40753</v>
       </c>
       <c r="E10" t="n">
-        <v>84382</v>
+        <v>88626</v>
       </c>
       <c r="F10" t="n">
         <v>71411</v>
       </c>
       <c r="G10" t="n">
-        <v>107920</v>
+        <v>112164</v>
       </c>
       <c r="H10" t="n">
-        <v>582</v>
+        <v>556</v>
       </c>
       <c r="I10" t="n">
-        <v>17068</v>
+        <v>17336</v>
       </c>
       <c r="J10" t="n">
-        <v>26634</v>
+        <v>28149</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0159</v>
+        <v>0.0136</v>
       </c>
       <c r="L10" t="n">
-        <v>0.239</v>
+        <v>0.2428</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2468</v>
+        <v>0.251</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>202510</v>
+        <v>202511</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20251001</t>
+          <t>20251101</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4879</v>
+        <v>4653</v>
       </c>
       <c r="D11" t="n">
-        <v>31856</v>
+        <v>36509</v>
       </c>
       <c r="E11" t="n">
-        <v>79729</v>
+        <v>84382</v>
       </c>
       <c r="F11" t="n">
         <v>71411</v>
       </c>
       <c r="G11" t="n">
-        <v>103267</v>
+        <v>107920</v>
       </c>
       <c r="H11" t="n">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="I11" t="n">
-        <v>16769</v>
+        <v>17068</v>
       </c>
       <c r="J11" t="n">
-        <v>25066</v>
+        <v>26634</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0179</v>
+        <v>0.0159</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2348</v>
+        <v>0.239</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2427</v>
+        <v>0.2468</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>202509</v>
+        <v>202510</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>20250901</t>
+          <t>20251001</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4479</v>
+        <v>4879</v>
       </c>
       <c r="D12" t="n">
-        <v>26977</v>
+        <v>31856</v>
       </c>
       <c r="E12" t="n">
-        <v>74850</v>
+        <v>79729</v>
       </c>
       <c r="F12" t="n">
         <v>71411</v>
       </c>
       <c r="G12" t="n">
-        <v>98388</v>
+        <v>103267</v>
       </c>
       <c r="H12" t="n">
-        <v>542</v>
+        <v>570</v>
       </c>
       <c r="I12" t="n">
-        <v>16420</v>
+        <v>16769</v>
       </c>
       <c r="J12" t="n">
-        <v>23482</v>
+        <v>25066</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0201</v>
+        <v>0.0179</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2299</v>
+        <v>0.2348</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2387</v>
+        <v>0.2427</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>202508</v>
+        <v>202509</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20250801</t>
+          <t>20250901</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4263</v>
+        <v>4479</v>
       </c>
       <c r="D13" t="n">
-        <v>22498</v>
+        <v>26977</v>
       </c>
       <c r="E13" t="n">
-        <v>70371</v>
+        <v>74850</v>
       </c>
       <c r="F13" t="n">
         <v>71411</v>
       </c>
       <c r="G13" t="n">
-        <v>93909</v>
+        <v>98388</v>
       </c>
       <c r="H13" t="n">
-        <v>458</v>
+        <v>542</v>
       </c>
       <c r="I13" t="n">
-        <v>16028</v>
+        <v>16420</v>
       </c>
       <c r="J13" t="n">
-        <v>21925</v>
+        <v>23482</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0204</v>
+        <v>0.0201</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2244</v>
+        <v>0.2299</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2335</v>
+        <v>0.2387</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>202507</v>
+        <v>202508</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20250701</t>
+          <t>20250801</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4305</v>
+        <v>4263</v>
       </c>
       <c r="D14" t="n">
-        <v>18235</v>
+        <v>22498</v>
       </c>
       <c r="E14" t="n">
-        <v>66108</v>
+        <v>70371</v>
       </c>
       <c r="F14" t="n">
         <v>71411</v>
       </c>
       <c r="G14" t="n">
-        <v>89646</v>
+        <v>93909</v>
       </c>
       <c r="H14" t="n">
-        <v>625</v>
+        <v>458</v>
       </c>
       <c r="I14" t="n">
-        <v>15583</v>
+        <v>16028</v>
       </c>
       <c r="J14" t="n">
-        <v>20431</v>
+        <v>21925</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0343</v>
+        <v>0.0204</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2182</v>
+        <v>0.2244</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2279</v>
+        <v>0.2335</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>202506</v>
+        <v>202507</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20250601</t>
+          <t>20250701</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3230</v>
+        <v>4305</v>
       </c>
       <c r="D15" t="n">
-        <v>13930</v>
+        <v>18235</v>
       </c>
       <c r="E15" t="n">
-        <v>61803</v>
+        <v>66108</v>
       </c>
       <c r="F15" t="n">
         <v>71411</v>
       </c>
       <c r="G15" t="n">
-        <v>85341</v>
+        <v>89646</v>
       </c>
       <c r="H15" t="n">
-        <v>375</v>
+        <v>625</v>
       </c>
       <c r="I15" t="n">
-        <v>15099</v>
+        <v>15583</v>
       </c>
       <c r="J15" t="n">
-        <v>18801</v>
+        <v>20431</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0269</v>
+        <v>0.0343</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2114</v>
+        <v>0.2182</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2203</v>
+        <v>0.2279</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>202505</v>
+        <v>202506</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20250501</t>
+          <t>20250601</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3260</v>
+        <v>3230</v>
       </c>
       <c r="D16" t="n">
-        <v>10700</v>
+        <v>13930</v>
       </c>
       <c r="E16" t="n">
-        <v>58573</v>
+        <v>61803</v>
       </c>
       <c r="F16" t="n">
         <v>71411</v>
       </c>
       <c r="G16" t="n">
-        <v>82111</v>
+        <v>85341</v>
       </c>
       <c r="H16" t="n">
-        <v>503</v>
+        <v>375</v>
       </c>
       <c r="I16" t="n">
-        <v>14560</v>
+        <v>15099</v>
       </c>
       <c r="J16" t="n">
-        <v>17457</v>
+        <v>18801</v>
       </c>
       <c r="K16" t="n">
-        <v>0.047</v>
+        <v>0.0269</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2039</v>
+        <v>0.2114</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2126</v>
+        <v>0.2203</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>202504</v>
+        <v>202505</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20250401</t>
+          <t>20250501</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1979</v>
+        <v>3260</v>
       </c>
       <c r="D17" t="n">
-        <v>7440</v>
+        <v>10700</v>
       </c>
       <c r="E17" t="n">
-        <v>55313</v>
+        <v>58573</v>
       </c>
       <c r="F17" t="n">
         <v>71411</v>
       </c>
       <c r="G17" t="n">
-        <v>78851</v>
+        <v>82111</v>
       </c>
       <c r="H17" t="n">
-        <v>250</v>
+        <v>503</v>
       </c>
       <c r="I17" t="n">
-        <v>13701</v>
+        <v>14560</v>
       </c>
       <c r="J17" t="n">
-        <v>15597</v>
+        <v>17457</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0336</v>
+        <v>0.047</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1919</v>
+        <v>0.2039</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1978</v>
+        <v>0.2126</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>202503</v>
+        <v>202504</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>20250301</t>
+          <t>20250401</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2016</v>
+        <v>1979</v>
       </c>
       <c r="D18" t="n">
-        <v>5461</v>
+        <v>7440</v>
       </c>
       <c r="E18" t="n">
-        <v>53334</v>
+        <v>55313</v>
       </c>
       <c r="F18" t="n">
         <v>71411</v>
       </c>
       <c r="G18" t="n">
-        <v>76872</v>
+        <v>78851</v>
       </c>
       <c r="H18" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="I18" t="n">
-        <v>12813</v>
+        <v>13701</v>
       </c>
       <c r="J18" t="n">
-        <v>14128</v>
+        <v>15597</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0476</v>
+        <v>0.0336</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1794</v>
+        <v>0.1919</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1838</v>
+        <v>0.1978</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>202502</v>
+        <v>202503</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20250201</t>
+          <t>20250301</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1717</v>
+        <v>2016</v>
       </c>
       <c r="D19" t="n">
-        <v>3445</v>
+        <v>5461</v>
       </c>
       <c r="E19" t="n">
-        <v>51318</v>
+        <v>53334</v>
       </c>
       <c r="F19" t="n">
         <v>71411</v>
       </c>
       <c r="G19" t="n">
-        <v>74856</v>
+        <v>76872</v>
       </c>
       <c r="H19" t="n">
-        <v>302</v>
+        <v>260</v>
       </c>
       <c r="I19" t="n">
-        <v>11551</v>
+        <v>12813</v>
       </c>
       <c r="J19" t="n">
-        <v>12345</v>
+        <v>14128</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0877</v>
+        <v>0.0476</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1618</v>
+        <v>0.1794</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1649</v>
+        <v>0.1838</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>202501</v>
+        <v>202502</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20250101</t>
+          <t>20250201</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1728</v>
+        <v>1717</v>
       </c>
       <c r="D20" t="n">
-        <v>1728</v>
+        <v>3445</v>
       </c>
       <c r="E20" t="n">
-        <v>49601</v>
+        <v>51318</v>
       </c>
       <c r="F20" t="n">
         <v>71411</v>
       </c>
       <c r="G20" t="n">
-        <v>73139</v>
+        <v>74856</v>
       </c>
       <c r="H20" t="n">
-        <v>319</v>
+        <v>302</v>
       </c>
       <c r="I20" t="n">
-        <v>9485</v>
+        <v>11551</v>
       </c>
       <c r="J20" t="n">
-        <v>9804</v>
+        <v>12345</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1846</v>
+        <v>0.0877</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1328</v>
+        <v>0.1618</v>
       </c>
       <c r="M20" t="n">
-        <v>0.134</v>
+        <v>0.1649</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>202412</v>
+        <v>202501</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20241201</t>
+          <t>20250101</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1667</v>
+        <v>1728</v>
       </c>
       <c r="D21" t="n">
-        <v>24407</v>
+        <v>1728</v>
       </c>
       <c r="E21" t="n">
-        <v>47873</v>
+        <v>49601</v>
       </c>
       <c r="F21" t="n">
-        <v>47004</v>
+        <v>71411</v>
       </c>
       <c r="G21" t="n">
-        <v>71411</v>
+        <v>73139</v>
       </c>
       <c r="H21" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I21" t="n">
-        <v>13215</v>
+        <v>9485</v>
       </c>
       <c r="J21" t="n">
-        <v>21568</v>
+        <v>9804</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0129</v>
+        <v>0.1846</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2811</v>
+        <v>0.1328</v>
       </c>
       <c r="M21" t="n">
-        <v>0.302</v>
+        <v>0.134</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>202411</v>
+        <v>202412</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20241101</t>
+          <t>20241201</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2316</v>
+        <v>1667</v>
       </c>
       <c r="D22" t="n">
-        <v>22740</v>
+        <v>24407</v>
       </c>
       <c r="E22" t="n">
-        <v>46206</v>
+        <v>47873</v>
       </c>
       <c r="F22" t="n">
         <v>47004</v>
       </c>
       <c r="G22" t="n">
-        <v>69744</v>
+        <v>71411</v>
       </c>
       <c r="H22" t="n">
-        <v>398</v>
+        <v>316</v>
       </c>
       <c r="I22" t="n">
-        <v>13003</v>
+        <v>13215</v>
       </c>
       <c r="J22" t="n">
-        <v>20490</v>
+        <v>21568</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0175</v>
+        <v>0.0129</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2766</v>
+        <v>0.2811</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2938</v>
+        <v>0.302</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>202410</v>
+        <v>202411</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20241001</t>
+          <t>20241101</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2602</v>
+        <v>2316</v>
       </c>
       <c r="D23" t="n">
-        <v>20424</v>
+        <v>22740</v>
       </c>
       <c r="E23" t="n">
-        <v>43890</v>
+        <v>46206</v>
       </c>
       <c r="F23" t="n">
         <v>47004</v>
       </c>
       <c r="G23" t="n">
-        <v>67428</v>
+        <v>69744</v>
       </c>
       <c r="H23" t="n">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="I23" t="n">
-        <v>12755</v>
+        <v>13003</v>
       </c>
       <c r="J23" t="n">
-        <v>19186</v>
+        <v>20490</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0192</v>
+        <v>0.0175</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2714</v>
+        <v>0.2766</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2845</v>
+        <v>0.2938</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>202409</v>
+        <v>202410</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20240901</t>
+          <t>20241001</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2428</v>
+        <v>2602</v>
       </c>
       <c r="D24" t="n">
-        <v>17822</v>
+        <v>20424</v>
       </c>
       <c r="E24" t="n">
-        <v>41288</v>
+        <v>43890</v>
       </c>
       <c r="F24" t="n">
         <v>47004</v>
       </c>
       <c r="G24" t="n">
-        <v>64826</v>
+        <v>67428</v>
       </c>
       <c r="H24" t="n">
-        <v>315</v>
+        <v>392</v>
       </c>
       <c r="I24" t="n">
-        <v>12473</v>
+        <v>12755</v>
       </c>
       <c r="J24" t="n">
-        <v>18013</v>
+        <v>19186</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0177</v>
+        <v>0.0192</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2654</v>
+        <v>0.2714</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2779</v>
+        <v>0.2845</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>202408</v>
+        <v>202409</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20240801</t>
+          <t>20240901</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2216</v>
+        <v>2428</v>
       </c>
       <c r="D25" t="n">
-        <v>15394</v>
+        <v>17822</v>
       </c>
       <c r="E25" t="n">
-        <v>38860</v>
+        <v>41288</v>
       </c>
       <c r="F25" t="n">
         <v>47004</v>
       </c>
       <c r="G25" t="n">
-        <v>62398</v>
+        <v>64826</v>
       </c>
       <c r="H25" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="I25" t="n">
-        <v>12168</v>
+        <v>12473</v>
       </c>
       <c r="J25" t="n">
-        <v>16926</v>
+        <v>18013</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0204</v>
+        <v>0.0177</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2589</v>
+        <v>0.2654</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2713</v>
+        <v>0.2779</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>202407</v>
+        <v>202408</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20240701</t>
+          <t>20240801</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1998</v>
+        <v>2216</v>
       </c>
       <c r="D26" t="n">
-        <v>13178</v>
+        <v>15394</v>
       </c>
       <c r="E26" t="n">
-        <v>36644</v>
+        <v>38860</v>
       </c>
       <c r="F26" t="n">
         <v>47004</v>
       </c>
       <c r="G26" t="n">
-        <v>60182</v>
+        <v>62398</v>
       </c>
       <c r="H26" t="n">
-        <v>286</v>
+        <v>314</v>
       </c>
       <c r="I26" t="n">
-        <v>11803</v>
+        <v>12168</v>
       </c>
       <c r="J26" t="n">
-        <v>15825</v>
+        <v>16926</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0217</v>
+        <v>0.0204</v>
       </c>
       <c r="L26" t="n">
-        <v>0.2511</v>
+        <v>0.2589</v>
       </c>
       <c r="M26" t="n">
-        <v>0.263</v>
+        <v>0.2713</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>202406</v>
+        <v>202407</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20240601</t>
+          <t>20240701</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1808</v>
+        <v>1998</v>
       </c>
       <c r="D27" t="n">
-        <v>11180</v>
+        <v>13178</v>
       </c>
       <c r="E27" t="n">
-        <v>34646</v>
+        <v>36644</v>
       </c>
       <c r="F27" t="n">
         <v>47004</v>
       </c>
       <c r="G27" t="n">
-        <v>58184</v>
+        <v>60182</v>
       </c>
       <c r="H27" t="n">
-        <v>246</v>
+        <v>286</v>
       </c>
       <c r="I27" t="n">
-        <v>11389</v>
+        <v>11803</v>
       </c>
       <c r="J27" t="n">
-        <v>14703</v>
+        <v>15825</v>
       </c>
       <c r="K27" t="n">
-        <v>0.022</v>
+        <v>0.0217</v>
       </c>
       <c r="L27" t="n">
-        <v>0.2423</v>
+        <v>0.2511</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2527</v>
+        <v>0.263</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>202405</v>
+        <v>202406</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20240501</t>
+          <t>20240601</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2185</v>
+        <v>1808</v>
       </c>
       <c r="D28" t="n">
-        <v>9372</v>
+        <v>11180</v>
       </c>
       <c r="E28" t="n">
-        <v>32838</v>
+        <v>34646</v>
       </c>
       <c r="F28" t="n">
         <v>47004</v>
       </c>
       <c r="G28" t="n">
-        <v>56376</v>
+        <v>58184</v>
       </c>
       <c r="H28" t="n">
-        <v>367</v>
+        <v>246</v>
       </c>
       <c r="I28" t="n">
-        <v>10931</v>
+        <v>11389</v>
       </c>
       <c r="J28" t="n">
-        <v>13647</v>
+        <v>14703</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0392</v>
+        <v>0.022</v>
       </c>
       <c r="L28" t="n">
-        <v>0.2326</v>
+        <v>0.2423</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2421</v>
+        <v>0.2527</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>202404</v>
+        <v>202405</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20240401</t>
+          <t>20240501</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2218</v>
+        <v>2185</v>
       </c>
       <c r="D29" t="n">
-        <v>7187</v>
+        <v>9372</v>
       </c>
       <c r="E29" t="n">
-        <v>30653</v>
+        <v>32838</v>
       </c>
       <c r="F29" t="n">
         <v>47004</v>
       </c>
       <c r="G29" t="n">
-        <v>54191</v>
+        <v>56376</v>
       </c>
       <c r="H29" t="n">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="I29" t="n">
-        <v>10391</v>
+        <v>10931</v>
       </c>
       <c r="J29" t="n">
-        <v>12346</v>
+        <v>13647</v>
       </c>
       <c r="K29" t="n">
-        <v>0.0522</v>
+        <v>0.0392</v>
       </c>
       <c r="L29" t="n">
-        <v>0.2211</v>
+        <v>0.2326</v>
       </c>
       <c r="M29" t="n">
-        <v>0.2278</v>
+        <v>0.2421</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>202403</v>
+        <v>202404</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20240301</t>
+          <t>20240401</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1804</v>
+        <v>2218</v>
       </c>
       <c r="D30" t="n">
-        <v>4969</v>
+        <v>7187</v>
       </c>
       <c r="E30" t="n">
-        <v>28435</v>
+        <v>30653</v>
       </c>
       <c r="F30" t="n">
         <v>47004</v>
       </c>
       <c r="G30" t="n">
-        <v>51973</v>
+        <v>54191</v>
       </c>
       <c r="H30" t="n">
-        <v>287</v>
+        <v>375</v>
       </c>
       <c r="I30" t="n">
-        <v>9674</v>
+        <v>10391</v>
       </c>
       <c r="J30" t="n">
-        <v>10937</v>
+        <v>12346</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0578</v>
+        <v>0.0522</v>
       </c>
       <c r="L30" t="n">
-        <v>0.2058</v>
+        <v>0.2211</v>
       </c>
       <c r="M30" t="n">
-        <v>0.2104</v>
+        <v>0.2278</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>202402</v>
+        <v>202403</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20240201</t>
+          <t>20240301</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1853</v>
+        <v>1804</v>
       </c>
       <c r="D31" t="n">
-        <v>3165</v>
+        <v>4969</v>
       </c>
       <c r="E31" t="n">
-        <v>26631</v>
+        <v>28435</v>
       </c>
       <c r="F31" t="n">
         <v>47004</v>
       </c>
       <c r="G31" t="n">
-        <v>50169</v>
+        <v>51973</v>
       </c>
       <c r="H31" t="n">
-        <v>345</v>
+        <v>287</v>
       </c>
       <c r="I31" t="n">
-        <v>8711</v>
+        <v>9674</v>
       </c>
       <c r="J31" t="n">
-        <v>9423</v>
+        <v>10937</v>
       </c>
       <c r="K31" t="n">
-        <v>0.109</v>
+        <v>0.0578</v>
       </c>
       <c r="L31" t="n">
-        <v>0.1853</v>
+        <v>0.2058</v>
       </c>
       <c r="M31" t="n">
-        <v>0.1878</v>
+        <v>0.2104</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>202401</v>
+        <v>202402</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20240101</t>
+          <t>20240201</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1312</v>
+        <v>1853</v>
       </c>
       <c r="D32" t="n">
-        <v>1312</v>
+        <v>3165</v>
       </c>
       <c r="E32" t="n">
-        <v>24778</v>
+        <v>26631</v>
       </c>
       <c r="F32" t="n">
         <v>47004</v>
       </c>
       <c r="G32" t="n">
-        <v>48316</v>
+        <v>50169</v>
       </c>
       <c r="H32" t="n">
-        <v>205</v>
+        <v>345</v>
       </c>
       <c r="I32" t="n">
-        <v>7145</v>
+        <v>8711</v>
       </c>
       <c r="J32" t="n">
-        <v>7350</v>
+        <v>9423</v>
       </c>
       <c r="K32" t="n">
-        <v>0.1563</v>
+        <v>0.109</v>
       </c>
       <c r="L32" t="n">
-        <v>0.152</v>
+        <v>0.1853</v>
       </c>
       <c r="M32" t="n">
-        <v>0.1521</v>
+        <v>0.1878</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>202312</v>
+        <v>202401</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20231201</t>
+          <t>20240101</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1283</v>
+        <v>1312</v>
       </c>
       <c r="D33" t="n">
-        <v>13224</v>
+        <v>1312</v>
       </c>
       <c r="E33" t="n">
-        <v>23466</v>
+        <v>24778</v>
       </c>
       <c r="F33" t="n">
-        <v>33780</v>
+        <v>47004</v>
       </c>
       <c r="G33" t="n">
-        <v>47004</v>
+        <v>48316</v>
       </c>
       <c r="H33" t="n">
-        <v>171</v>
+        <v>205</v>
       </c>
       <c r="I33" t="n">
-        <v>10305</v>
+        <v>7145</v>
       </c>
       <c r="J33" t="n">
-        <v>15974</v>
+        <v>7350</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0129</v>
+        <v>0.1563</v>
       </c>
       <c r="L33" t="n">
-        <v>0.3051</v>
+        <v>0.152</v>
       </c>
       <c r="M33" t="n">
-        <v>0.3398</v>
+        <v>0.1521</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>202311</v>
+        <v>202312</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20231101</t>
+          <t>20231201</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1419</v>
+        <v>1283</v>
       </c>
       <c r="D34" t="n">
-        <v>11941</v>
+        <v>13224</v>
       </c>
       <c r="E34" t="n">
-        <v>22183</v>
+        <v>23466</v>
       </c>
       <c r="F34" t="n">
         <v>33780</v>
       </c>
       <c r="G34" t="n">
-        <v>45721</v>
+        <v>47004</v>
       </c>
       <c r="H34" t="n">
-        <v>224</v>
+        <v>171</v>
       </c>
       <c r="I34" t="n">
-        <v>10153</v>
+        <v>10305</v>
       </c>
       <c r="J34" t="n">
-        <v>15272</v>
+        <v>15974</v>
       </c>
       <c r="K34" t="n">
-        <v>0.0188</v>
+        <v>0.0129</v>
       </c>
       <c r="L34" t="n">
-        <v>0.3006</v>
+        <v>0.3051</v>
       </c>
       <c r="M34" t="n">
-        <v>0.334</v>
+        <v>0.3398</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>202310</v>
+        <v>202311</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20231001</t>
+          <t>20231101</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1370</v>
+        <v>1419</v>
       </c>
       <c r="D35" t="n">
-        <v>10522</v>
+        <v>11941</v>
       </c>
       <c r="E35" t="n">
-        <v>20764</v>
+        <v>22183</v>
       </c>
       <c r="F35" t="n">
         <v>33780</v>
       </c>
       <c r="G35" t="n">
-        <v>44302</v>
+        <v>45721</v>
       </c>
       <c r="H35" t="n">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="I35" t="n">
-        <v>9964</v>
+        <v>10153</v>
       </c>
       <c r="J35" t="n">
-        <v>14471</v>
+        <v>15272</v>
       </c>
       <c r="K35" t="n">
-        <v>0.0194</v>
+        <v>0.0188</v>
       </c>
       <c r="L35" t="n">
-        <v>0.295</v>
+        <v>0.3006</v>
       </c>
       <c r="M35" t="n">
-        <v>0.3266</v>
+        <v>0.334</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>202309</v>
+        <v>202310</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20230901</t>
+          <t>20231001</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1352</v>
+        <v>1370</v>
       </c>
       <c r="D36" t="n">
-        <v>9152</v>
+        <v>10522</v>
       </c>
       <c r="E36" t="n">
-        <v>19394</v>
+        <v>20764</v>
       </c>
       <c r="F36" t="n">
         <v>33780</v>
       </c>
       <c r="G36" t="n">
-        <v>42932</v>
+        <v>44302</v>
       </c>
       <c r="H36" t="n">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="I36" t="n">
-        <v>9730</v>
+        <v>9964</v>
       </c>
       <c r="J36" t="n">
-        <v>13676</v>
+        <v>14471</v>
       </c>
       <c r="K36" t="n">
-        <v>0.0267</v>
+        <v>0.0194</v>
       </c>
       <c r="L36" t="n">
-        <v>0.288</v>
+        <v>0.295</v>
       </c>
       <c r="M36" t="n">
-        <v>0.3186</v>
+        <v>0.3266</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>202308</v>
+        <v>202309</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20230801</t>
+          <t>20230901</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1071</v>
+        <v>1352</v>
       </c>
       <c r="D37" t="n">
-        <v>7800</v>
+        <v>9152</v>
       </c>
       <c r="E37" t="n">
-        <v>18042</v>
+        <v>19394</v>
       </c>
       <c r="F37" t="n">
         <v>33780</v>
       </c>
       <c r="G37" t="n">
-        <v>41580</v>
+        <v>42932</v>
       </c>
       <c r="H37" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="I37" t="n">
-        <v>9509</v>
+        <v>9730</v>
       </c>
       <c r="J37" t="n">
-        <v>12877</v>
+        <v>13676</v>
       </c>
       <c r="K37" t="n">
-        <v>0.031</v>
+        <v>0.0267</v>
       </c>
       <c r="L37" t="n">
-        <v>0.2815</v>
+        <v>0.288</v>
       </c>
       <c r="M37" t="n">
-        <v>0.3097</v>
+        <v>0.3186</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>202307</v>
+        <v>202308</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20230701</t>
+          <t>20230801</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>943</v>
+        <v>1071</v>
       </c>
       <c r="D38" t="n">
-        <v>6729</v>
+        <v>7800</v>
       </c>
       <c r="E38" t="n">
-        <v>16971</v>
+        <v>18042</v>
       </c>
       <c r="F38" t="n">
         <v>33780</v>
       </c>
       <c r="G38" t="n">
-        <v>40509</v>
+        <v>41580</v>
       </c>
       <c r="H38" t="n">
-        <v>191</v>
+        <v>242</v>
       </c>
       <c r="I38" t="n">
-        <v>9199</v>
+        <v>9509</v>
       </c>
       <c r="J38" t="n">
-        <v>11983</v>
+        <v>12877</v>
       </c>
       <c r="K38" t="n">
-        <v>0.0284</v>
+        <v>0.031</v>
       </c>
       <c r="L38" t="n">
-        <v>0.2723</v>
+        <v>0.2815</v>
       </c>
       <c r="M38" t="n">
-        <v>0.2958</v>
+        <v>0.3097</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>202306</v>
+        <v>202307</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20230601</t>
+          <t>20230701</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>997</v>
+        <v>943</v>
       </c>
       <c r="D39" t="n">
-        <v>5786</v>
+        <v>6729</v>
       </c>
       <c r="E39" t="n">
-        <v>16028</v>
+        <v>16971</v>
       </c>
       <c r="F39" t="n">
         <v>33780</v>
       </c>
       <c r="G39" t="n">
-        <v>39566</v>
+        <v>40509</v>
       </c>
       <c r="H39" t="n">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="I39" t="n">
-        <v>8898</v>
+        <v>9199</v>
       </c>
       <c r="J39" t="n">
-        <v>11195</v>
+        <v>11983</v>
       </c>
       <c r="K39" t="n">
-        <v>0.0363</v>
+        <v>0.0284</v>
       </c>
       <c r="L39" t="n">
-        <v>0.2634</v>
+        <v>0.2723</v>
       </c>
       <c r="M39" t="n">
-        <v>0.2829</v>
+        <v>0.2958</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>202305</v>
+        <v>202306</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20230501</t>
+          <t>20230601</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>925</v>
+        <v>997</v>
       </c>
       <c r="D40" t="n">
-        <v>4789</v>
+        <v>5786</v>
       </c>
       <c r="E40" t="n">
-        <v>15031</v>
+        <v>16028</v>
       </c>
       <c r="F40" t="n">
         <v>33780</v>
       </c>
       <c r="G40" t="n">
-        <v>38569</v>
+        <v>39566</v>
       </c>
       <c r="H40" t="n">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="I40" t="n">
-        <v>8553</v>
+        <v>8898</v>
       </c>
       <c r="J40" t="n">
-        <v>10381</v>
+        <v>11195</v>
       </c>
       <c r="K40" t="n">
-        <v>0.0407</v>
+        <v>0.0363</v>
       </c>
       <c r="L40" t="n">
-        <v>0.2532</v>
+        <v>0.2634</v>
       </c>
       <c r="M40" t="n">
-        <v>0.2692</v>
+        <v>0.2829</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>202304</v>
+        <v>202305</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20230401</t>
+          <t>20230501</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>908</v>
+        <v>925</v>
       </c>
       <c r="D41" t="n">
-        <v>3864</v>
+        <v>4789</v>
       </c>
       <c r="E41" t="n">
-        <v>14106</v>
+        <v>15031</v>
       </c>
       <c r="F41" t="n">
         <v>33780</v>
       </c>
       <c r="G41" t="n">
-        <v>37644</v>
+        <v>38569</v>
       </c>
       <c r="H41" t="n">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="I41" t="n">
-        <v>8105</v>
+        <v>8553</v>
       </c>
       <c r="J41" t="n">
-        <v>9507</v>
+        <v>10381</v>
       </c>
       <c r="K41" t="n">
-        <v>0.0531</v>
+        <v>0.0407</v>
       </c>
       <c r="L41" t="n">
-        <v>0.2399</v>
+        <v>0.2532</v>
       </c>
       <c r="M41" t="n">
-        <v>0.2526</v>
+        <v>0.2692</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>202303</v>
+        <v>202304</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>20230301</t>
+          <t>20230401</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1082</v>
+        <v>908</v>
       </c>
       <c r="D42" t="n">
-        <v>2956</v>
+        <v>3864</v>
       </c>
       <c r="E42" t="n">
-        <v>13198</v>
+        <v>14106</v>
       </c>
       <c r="F42" t="n">
         <v>33780</v>
       </c>
       <c r="G42" t="n">
-        <v>36736</v>
+        <v>37644</v>
       </c>
       <c r="H42" t="n">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="I42" t="n">
-        <v>7570</v>
+        <v>8105</v>
       </c>
       <c r="J42" t="n">
-        <v>8534</v>
+        <v>9507</v>
       </c>
       <c r="K42" t="n">
-        <v>0.07439999999999999</v>
+        <v>0.0531</v>
       </c>
       <c r="L42" t="n">
-        <v>0.2241</v>
+        <v>0.2399</v>
       </c>
       <c r="M42" t="n">
-        <v>0.2323</v>
+        <v>0.2526</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>202302</v>
+        <v>202303</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>20230201</t>
+          <t>20230301</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>973</v>
+        <v>1082</v>
       </c>
       <c r="D43" t="n">
-        <v>1874</v>
+        <v>2956</v>
       </c>
       <c r="E43" t="n">
-        <v>12116</v>
+        <v>13198</v>
       </c>
       <c r="F43" t="n">
         <v>33780</v>
       </c>
       <c r="G43" t="n">
-        <v>35654</v>
+        <v>36736</v>
       </c>
       <c r="H43" t="n">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="I43" t="n">
-        <v>6720</v>
+        <v>7570</v>
       </c>
       <c r="J43" t="n">
-        <v>7265</v>
+        <v>8534</v>
       </c>
       <c r="K43" t="n">
-        <v>0.1099</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="L43" t="n">
-        <v>0.1989</v>
+        <v>0.2241</v>
       </c>
       <c r="M43" t="n">
-        <v>0.2038</v>
+        <v>0.2323</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>202301</v>
+        <v>202302</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>20230101</t>
+          <t>20230201</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>901</v>
+        <v>973</v>
       </c>
       <c r="D44" t="n">
-        <v>901</v>
+        <v>1874</v>
       </c>
       <c r="E44" t="n">
-        <v>11143</v>
+        <v>12116</v>
       </c>
       <c r="F44" t="n">
         <v>33780</v>
       </c>
       <c r="G44" t="n">
-        <v>34681</v>
+        <v>35654</v>
       </c>
       <c r="H44" t="n">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="I44" t="n">
-        <v>5489</v>
+        <v>6720</v>
       </c>
       <c r="J44" t="n">
-        <v>5677</v>
+        <v>7265</v>
       </c>
       <c r="K44" t="n">
-        <v>0.2087</v>
+        <v>0.1099</v>
       </c>
       <c r="L44" t="n">
-        <v>0.1625</v>
+        <v>0.1989</v>
       </c>
       <c r="M44" t="n">
-        <v>0.1637</v>
+        <v>0.2038</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>202212</v>
+        <v>202301</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20221201</t>
+          <t>20230101</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>691</v>
+        <v>901</v>
       </c>
       <c r="D45" t="n">
-        <v>10242</v>
+        <v>901</v>
       </c>
       <c r="E45" t="n">
-        <v>10242</v>
+        <v>11143</v>
       </c>
       <c r="F45" t="n">
-        <v>23538</v>
+        <v>33780</v>
       </c>
       <c r="G45" t="n">
-        <v>33780</v>
+        <v>34681</v>
       </c>
       <c r="H45" t="n">
-        <v>135</v>
+        <v>188</v>
       </c>
       <c r="I45" t="n">
-        <v>8031</v>
+        <v>5489</v>
       </c>
       <c r="J45" t="n">
-        <v>12349</v>
+        <v>5677</v>
       </c>
       <c r="K45" t="n">
-        <v>0.0132</v>
+        <v>0.2087</v>
       </c>
       <c r="L45" t="n">
-        <v>0.3412</v>
+        <v>0.1625</v>
       </c>
       <c r="M45" t="n">
-        <v>0.3656</v>
+        <v>0.1637</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>202211</v>
+        <v>202212</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>20221101</t>
+          <t>20221201</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1040</v>
+        <v>691</v>
       </c>
       <c r="D46" t="n">
-        <v>9551</v>
+        <v>10242</v>
       </c>
       <c r="E46" t="n">
-        <v>9551</v>
+        <v>10242</v>
       </c>
       <c r="F46" t="n">
         <v>23538</v>
       </c>
       <c r="G46" t="n">
-        <v>33089</v>
+        <v>33780</v>
       </c>
       <c r="H46" t="n">
-        <v>215</v>
+        <v>135</v>
       </c>
       <c r="I46" t="n">
-        <v>7899</v>
+        <v>8031</v>
       </c>
       <c r="J46" t="n">
-        <v>11818</v>
+        <v>12349</v>
       </c>
       <c r="K46" t="n">
-        <v>0.0225</v>
+        <v>0.0132</v>
       </c>
       <c r="L46" t="n">
-        <v>0.3356</v>
+        <v>0.3412</v>
       </c>
       <c r="M46" t="n">
-        <v>0.3572</v>
+        <v>0.3656</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>202210</v>
+        <v>202211</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>20221001</t>
+          <t>20221101</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>961</v>
+        <v>1040</v>
       </c>
       <c r="D47" t="n">
-        <v>8511</v>
+        <v>9551</v>
       </c>
       <c r="E47" t="n">
-        <v>8511</v>
+        <v>9551</v>
       </c>
       <c r="F47" t="n">
         <v>23538</v>
       </c>
       <c r="G47" t="n">
-        <v>32049</v>
+        <v>33089</v>
       </c>
       <c r="H47" t="n">
-        <v>180</v>
+        <v>215</v>
       </c>
       <c r="I47" t="n">
-        <v>7732</v>
+        <v>7899</v>
       </c>
       <c r="J47" t="n">
-        <v>11120</v>
+        <v>11818</v>
       </c>
       <c r="K47" t="n">
-        <v>0.0211</v>
+        <v>0.0225</v>
       </c>
       <c r="L47" t="n">
-        <v>0.3285</v>
+        <v>0.3356</v>
       </c>
       <c r="M47" t="n">
-        <v>0.347</v>
+        <v>0.3572</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>202209</v>
+        <v>202210</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20220901</t>
+          <t>20221001</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1027</v>
+        <v>961</v>
       </c>
       <c r="D48" t="n">
-        <v>7550</v>
+        <v>8511</v>
       </c>
       <c r="E48" t="n">
-        <v>7550</v>
+        <v>8511</v>
       </c>
       <c r="F48" t="n">
         <v>23538</v>
       </c>
       <c r="G48" t="n">
-        <v>31088</v>
+        <v>32049</v>
       </c>
       <c r="H48" t="n">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="I48" t="n">
-        <v>7561</v>
+        <v>7732</v>
       </c>
       <c r="J48" t="n">
-        <v>10521</v>
+        <v>11120</v>
       </c>
       <c r="K48" t="n">
-        <v>0.0246</v>
+        <v>0.0211</v>
       </c>
       <c r="L48" t="n">
-        <v>0.3212</v>
+        <v>0.3285</v>
       </c>
       <c r="M48" t="n">
-        <v>0.3384</v>
+        <v>0.347</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>202208</v>
+        <v>202209</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20220801</t>
+          <t>20220901</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1048</v>
+        <v>1027</v>
       </c>
       <c r="D49" t="n">
-        <v>6523</v>
+        <v>7550</v>
       </c>
       <c r="E49" t="n">
-        <v>6523</v>
+        <v>7550</v>
       </c>
       <c r="F49" t="n">
         <v>23538</v>
       </c>
       <c r="G49" t="n">
-        <v>30061</v>
+        <v>31088</v>
       </c>
       <c r="H49" t="n">
-        <v>211</v>
+        <v>186</v>
       </c>
       <c r="I49" t="n">
-        <v>7365</v>
+        <v>7561</v>
       </c>
       <c r="J49" t="n">
-        <v>9899</v>
+        <v>10521</v>
       </c>
       <c r="K49" t="n">
-        <v>0.0323</v>
+        <v>0.0246</v>
       </c>
       <c r="L49" t="n">
-        <v>0.3129</v>
+        <v>0.3212</v>
       </c>
       <c r="M49" t="n">
-        <v>0.3293</v>
+        <v>0.3384</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>202207</v>
+        <v>202208</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>20220701</t>
+          <t>20220801</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>807</v>
+        <v>1048</v>
       </c>
       <c r="D50" t="n">
-        <v>5475</v>
+        <v>6523</v>
       </c>
       <c r="E50" t="n">
-        <v>5475</v>
+        <v>6523</v>
       </c>
       <c r="F50" t="n">
         <v>23538</v>
       </c>
       <c r="G50" t="n">
-        <v>29013</v>
+        <v>30061</v>
       </c>
       <c r="H50" t="n">
-        <v>165</v>
+        <v>211</v>
       </c>
       <c r="I50" t="n">
-        <v>7140</v>
+        <v>7365</v>
       </c>
       <c r="J50" t="n">
-        <v>9260</v>
+        <v>9899</v>
       </c>
       <c r="K50" t="n">
-        <v>0.0301</v>
+        <v>0.0323</v>
       </c>
       <c r="L50" t="n">
-        <v>0.3033</v>
+        <v>0.3129</v>
       </c>
       <c r="M50" t="n">
-        <v>0.3192</v>
+        <v>0.3293</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>202206</v>
+        <v>202207</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>20220601</t>
+          <t>20220701</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>792</v>
+        <v>807</v>
       </c>
       <c r="D51" t="n">
-        <v>4668</v>
+        <v>5475</v>
       </c>
       <c r="E51" t="n">
-        <v>4668</v>
+        <v>5475</v>
       </c>
       <c r="F51" t="n">
         <v>23538</v>
       </c>
       <c r="G51" t="n">
-        <v>28206</v>
+        <v>29013</v>
       </c>
       <c r="H51" t="n">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="I51" t="n">
-        <v>6915</v>
+        <v>7140</v>
       </c>
       <c r="J51" t="n">
-        <v>8689</v>
+        <v>9260</v>
       </c>
       <c r="K51" t="n">
-        <v>0.0381</v>
+        <v>0.0301</v>
       </c>
       <c r="L51" t="n">
-        <v>0.2938</v>
+        <v>0.3033</v>
       </c>
       <c r="M51" t="n">
-        <v>0.3081</v>
+        <v>0.3192</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>202205</v>
+        <v>202206</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20220501</t>
+          <t>20220601</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>820</v>
+        <v>792</v>
       </c>
       <c r="D52" t="n">
-        <v>3876</v>
+        <v>4668</v>
       </c>
       <c r="E52" t="n">
-        <v>3876</v>
+        <v>4668</v>
       </c>
       <c r="F52" t="n">
         <v>23538</v>
       </c>
       <c r="G52" t="n">
-        <v>27414</v>
+        <v>28206</v>
       </c>
       <c r="H52" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I52" t="n">
-        <v>6614</v>
+        <v>6915</v>
       </c>
       <c r="J52" t="n">
-        <v>8016</v>
+        <v>8689</v>
       </c>
       <c r="K52" t="n">
-        <v>0.0454</v>
+        <v>0.0381</v>
       </c>
       <c r="L52" t="n">
-        <v>0.281</v>
+        <v>0.2938</v>
       </c>
       <c r="M52" t="n">
-        <v>0.2924</v>
+        <v>0.3081</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>202204</v>
+        <v>202205</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>20220401</t>
+          <t>20220501</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>746</v>
+        <v>820</v>
       </c>
       <c r="D53" t="n">
-        <v>3056</v>
+        <v>3876</v>
       </c>
       <c r="E53" t="n">
-        <v>3056</v>
+        <v>3876</v>
       </c>
       <c r="F53" t="n">
         <v>23538</v>
       </c>
       <c r="G53" t="n">
-        <v>26594</v>
+        <v>27414</v>
       </c>
       <c r="H53" t="n">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="I53" t="n">
-        <v>6240</v>
+        <v>6614</v>
       </c>
       <c r="J53" t="n">
-        <v>7300</v>
+        <v>8016</v>
       </c>
       <c r="K53" t="n">
-        <v>0.0504</v>
+        <v>0.0454</v>
       </c>
       <c r="L53" t="n">
-        <v>0.2651</v>
+        <v>0.281</v>
       </c>
       <c r="M53" t="n">
-        <v>0.2745</v>
+        <v>0.2924</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>202203</v>
+        <v>202204</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>20220301</t>
+          <t>20220401</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>943</v>
+        <v>746</v>
       </c>
       <c r="D54" t="n">
-        <v>2310</v>
+        <v>3056</v>
       </c>
       <c r="E54" t="n">
-        <v>2310</v>
+        <v>3056</v>
       </c>
       <c r="F54" t="n">
         <v>23538</v>
       </c>
       <c r="G54" t="n">
-        <v>25848</v>
+        <v>26594</v>
       </c>
       <c r="H54" t="n">
-        <v>193</v>
+        <v>154</v>
       </c>
       <c r="I54" t="n">
-        <v>5823</v>
+        <v>6240</v>
       </c>
       <c r="J54" t="n">
-        <v>6585</v>
+        <v>7300</v>
       </c>
       <c r="K54" t="n">
-        <v>0.0835</v>
+        <v>0.0504</v>
       </c>
       <c r="L54" t="n">
-        <v>0.2474</v>
+        <v>0.2651</v>
       </c>
       <c r="M54" t="n">
-        <v>0.2548</v>
+        <v>0.2745</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>202202</v>
+        <v>202203</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>20220201</t>
+          <t>20220301</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>739</v>
+        <v>943</v>
       </c>
       <c r="D55" t="n">
-        <v>1367</v>
+        <v>2310</v>
       </c>
       <c r="E55" t="n">
-        <v>1367</v>
+        <v>2310</v>
       </c>
       <c r="F55" t="n">
         <v>23538</v>
       </c>
       <c r="G55" t="n">
-        <v>24905</v>
+        <v>25848</v>
       </c>
       <c r="H55" t="n">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="I55" t="n">
-        <v>5146</v>
+        <v>5823</v>
       </c>
       <c r="J55" t="n">
-        <v>5561</v>
+        <v>6585</v>
       </c>
       <c r="K55" t="n">
-        <v>0.1331</v>
+        <v>0.0835</v>
       </c>
       <c r="L55" t="n">
-        <v>0.2186</v>
+        <v>0.2474</v>
       </c>
       <c r="M55" t="n">
-        <v>0.2233</v>
+        <v>0.2548</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>202201</v>
+        <v>202202</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>20220101</t>
+          <t>20220201</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>628</v>
+        <v>739</v>
       </c>
       <c r="D56" t="n">
-        <v>628</v>
+        <v>1367</v>
       </c>
       <c r="E56" t="n">
-        <v>628</v>
+        <v>1367</v>
       </c>
       <c r="F56" t="n">
         <v>23538</v>
       </c>
       <c r="G56" t="n">
+        <v>24905</v>
+      </c>
+      <c r="H56" t="n">
+        <v>182</v>
+      </c>
+      <c r="I56" t="n">
+        <v>5146</v>
+      </c>
+      <c r="J56" t="n">
+        <v>5561</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.1331</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.2186</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.2233</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>202201</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>20220101</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>628</v>
+      </c>
+      <c r="D57" t="n">
+        <v>628</v>
+      </c>
+      <c r="E57" t="n">
+        <v>628</v>
+      </c>
+      <c r="F57" t="n">
+        <v>23538</v>
+      </c>
+      <c r="G57" t="n">
         <v>24166</v>
       </c>
-      <c r="H56" t="n">
+      <c r="H57" t="n">
         <v>145</v>
       </c>
-      <c r="I56" t="n">
+      <c r="I57" t="n">
         <v>4167</v>
       </c>
-      <c r="J56" t="n">
+      <c r="J57" t="n">
         <v>4312</v>
       </c>
-      <c r="K56" t="n">
+      <c r="K57" t="n">
         <v>0.2309</v>
       </c>
-      <c r="L56" t="n">
+      <c r="L57" t="n">
         <v>0.177</v>
       </c>
-      <c r="M56" t="n">
+      <c r="M57" t="n">
         <v>0.1784</v>
       </c>
     </row>
